--- a/tools/importer/reports/import-contact.report.xlsx
+++ b/tools/importer/reports/import-contact.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="673">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,6 +19,15 @@
     <t>blocks</t>
   </si>
   <si>
+    <t>captured</t>
+  </si>
+  <si>
+    <t>contacts</t>
+  </si>
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
     <t>path</t>
   </si>
   <si>
@@ -37,46 +46,127 @@
     <t>url</t>
   </si>
   <si>
+    <t>because-life.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-withimg","hero-minimal-dark-withimg","cards-minimal-dark-withimg-icons","cards-minimal-dark-withimg","columns-minimal-dark","columns-minimal-dark"]</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>because-life</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>campaign-landing</t>
+  </si>
+  <si>
+    <t>2026-10-07T08:36:16.065Z</t>
+  </si>
+  <si>
+    <t>Why Highmark? Because Life.™ | Reimagining Health Care</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/because-life</t>
+  </si>
+  <si>
     <t>contact.report.json</t>
   </si>
   <si>
+    <t>["form-minimal-light"]</t>
+  </si>
+  <si>
+    <t>contact</t>
+  </si>
+  <si>
+    <t>2026-10-14T08:30:32.469Z</t>
+  </si>
+  <si>
+    <t>Contact Highmark</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/contact?zg=false</t>
+  </si>
+  <si>
+    <t>employer.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-withimg","cards-minimal-dark-withimg-icons","columns-minimal-dark","columns-minimal-dark","columns-minimal-dark"]</t>
+  </si>
+  <si>
+    <t>employer</t>
+  </si>
+  <si>
+    <t>employer-landing</t>
+  </si>
+  <si>
+    <t>2026-09-30T20:30:12.433Z</t>
+  </si>
+  <si>
+    <t>Boost Employee Health and Save Money with Highmark Employer Plans</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/employer?zg=false</t>
+  </si>
+  <si>
+    <t>fraud-thank-you.report.json</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
-    <t>contact</t>
-  </si>
-  <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>2026-10-01T13:20:28.485Z</t>
-  </si>
-  <si>
-    <t>Contact Highmark</t>
-  </si>
-  <si>
-    <t>https://www.highmark.com/contact?zg=false</t>
-  </si>
-  <si>
-    <t>employer.report.json</t>
-  </si>
-  <si>
-    <t>["hero-minimal-dark-withimg","cards-minimal-dark-withimg-icons","columns-minimal-dark","columns-minimal-dark","columns-minimal-dark"]</t>
-  </si>
-  <si>
-    <t>employer</t>
-  </si>
-  <si>
-    <t>employer-landing</t>
-  </si>
-  <si>
-    <t>2026-09-30T20:30:12.433Z</t>
-  </si>
-  <si>
-    <t>Boost Employee Health and Save Money with Highmark Employer Plans</t>
-  </si>
-  <si>
-    <t>https://www.highmark.com/employer?zg=false</t>
+    <t>fraud-thank-you</t>
+  </si>
+  <si>
+    <t>2026-10-14T07:13:24.168Z</t>
+  </si>
+  <si>
+    <t>Thank You for Your Submission</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/fraud-thank-you</t>
+  </si>
+  <si>
+    <t>health-options-de.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-withimg","hero-minimal-dark-withimg","cards-minimal-dark-withimg","columns-minimal-dark","columns-minimal-dark","cards-minimal-dark-withimg-2"]</t>
+  </si>
+  <si>
+    <t>health-options-de</t>
+  </si>
+  <si>
+    <t>subsidiary-home</t>
+  </si>
+  <si>
+    <t>2026-10-07T07:59:49.094Z</t>
+  </si>
+  <si>
+    <t>Highmark Health Options - Delaware | HHO DE</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/health-options-de</t>
+  </si>
+  <si>
+    <t>health-options-wv.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-withimg","cards-minimal-dark-withimg","columns-minimal-dark","cards-minimal-dark-withimg-2"]</t>
+  </si>
+  <si>
+    <t>health-options-wv</t>
+  </si>
+  <si>
+    <t>2026-10-07T08:36:22.103Z</t>
+  </si>
+  <si>
+    <t>Highmark Health Options - West Virginia | HHO WV</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/health-options-wv</t>
   </si>
   <si>
     <t>index.report.json</t>
@@ -106,7 +196,7 @@
     <t>language-assistance</t>
   </si>
   <si>
-    <t>2026-10-01T13:19:19.820Z</t>
+    <t>2026-10-01T13:32:59.411Z</t>
   </si>
   <si>
     <t>Language Assistance</t>
@@ -115,12 +205,57 @@
     <t>https://www.highmark.com/language-assistance?zg=false</t>
   </si>
   <si>
+    <t>medicare-hra.report.json</t>
+  </si>
+  <si>
+    <t>medicare-hra</t>
+  </si>
+  <si>
+    <t>2026-10-05T15:02:48.379Z</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/medicare-hra</t>
+  </si>
+  <si>
+    <t>podcast.report.json</t>
+  </si>
+  <si>
+    <t>["columns-minimal-dark","columns-minimal-dark"]</t>
+  </si>
+  <si>
+    <t>podcast</t>
+  </si>
+  <si>
+    <t>content-landing</t>
+  </si>
+  <si>
+    <t>2026-10-05T15:24:27.479Z</t>
+  </si>
+  <si>
+    <t>Hitting a Higher Mark: Highmark Health Podcast</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/podcast</t>
+  </si>
+  <si>
+    <t>public-policy.report.json</t>
+  </si>
+  <si>
+    <t>public-policy</t>
+  </si>
+  <si>
+    <t>2026-10-05T15:24:33.681Z</t>
+  </si>
+  <si>
+    <t>Highmark's Public Policy</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/public-policy</t>
+  </si>
+  <si>
     <t>resources.report.json</t>
   </si>
   <si>
-    <t>["hero-minimal-dark-withimg","cards-minimal-dark-withimg","columns-minimal-dark","cards-minimal-dark-withimg-2"]</t>
-  </si>
-  <si>
     <t>resources</t>
   </si>
   <si>
@@ -136,6 +271,57 @@
     <t>https://www.highmark.com/resources</t>
   </si>
   <si>
+    <t>ventures.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-withimg","columns-minimal-dark","columns-minimal-dark"]</t>
+  </si>
+  <si>
+    <t>ventures</t>
+  </si>
+  <si>
+    <t>2026-10-07T08:36:26.595Z</t>
+  </si>
+  <si>
+    <t>Highmark Ventures: Transforming Healthcare</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/ventures</t>
+  </si>
+  <si>
+    <t>wholecare.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-withimg","hero-minimal-dark-withimg","cards-minimal-dark-withimg","columns-minimal-dark","cards-minimal-dark-withimg-2"]</t>
+  </si>
+  <si>
+    <t>wholecare</t>
+  </si>
+  <si>
+    <t>2026-10-07T07:59:54.475Z</t>
+  </si>
+  <si>
+    <t>Pennsylvania Medicaid and Medicare Insurance | Highmark Wholecare</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/wholecare</t>
+  </si>
+  <si>
+    <t>zipcode-gate-login.report.json</t>
+  </si>
+  <si>
+    <t>["zip-county-form","accordion-minimal-light"]</t>
+  </si>
+  <si>
+    <t>zipcode-gate-login</t>
+  </si>
+  <si>
+    <t>2026-10-06T11:01:05.594Z</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/zipcode-gate-login</t>
+  </si>
+  <si>
     <t>about/corporate-responsibility.report.json</t>
   </si>
   <si>
@@ -157,6 +343,27 @@
     <t>https://www.highmark.com/about/corporate-responsibility?zg=false</t>
   </si>
   <si>
+    <t>about/events.report.json</t>
+  </si>
+  <si>
+    <t>["press-release-list"]</t>
+  </si>
+  <si>
+    <t>about/events</t>
+  </si>
+  <si>
+    <t>events</t>
+  </si>
+  <si>
+    <t>2026-10-06T12:50:52.092Z</t>
+  </si>
+  <si>
+    <t>Highmark Events</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/events</t>
+  </si>
+  <si>
     <t>about/our-story.report.json</t>
   </si>
   <si>
@@ -172,6 +379,24 @@
     <t>https://www.highmark.com/about/our-story?zg=false</t>
   </si>
   <si>
+    <t>because-life/south-park-activities.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-withimg","cards-minimal-dark-withimg"]</t>
+  </si>
+  <si>
+    <t>because-life/south-park-activities</t>
+  </si>
+  <si>
+    <t>2026-10-07T13:26:13.789Z</t>
+  </si>
+  <si>
+    <t>South Park Activities Near Pittsburgh PA</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/because-life/south-park-activities</t>
+  </si>
+  <si>
     <t>employer/care-management.report.json</t>
   </si>
   <si>
@@ -265,6 +490,42 @@
     <t>https://www.highmark.com/employer/thought-leadership?zg=false</t>
   </si>
   <si>
+    <t>fraud/fraud-form.report.json</t>
+  </si>
+  <si>
+    <t>["cards-minimal-light-sidenav","cards-minimal-light-sidenav","form-minimal-light"]</t>
+  </si>
+  <si>
+    <t>fraud/fraud-form</t>
+  </si>
+  <si>
+    <t>fraud-form</t>
+  </si>
+  <si>
+    <t>2026-10-14T07:13:19.046Z</t>
+  </si>
+  <si>
+    <t>Health Care Fraud Form</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/fraud/fraud-form</t>
+  </si>
+  <si>
+    <t>modals/request-interview.report.json</t>
+  </si>
+  <si>
+    <t>modals/request-interview</t>
+  </si>
+  <si>
+    <t>2026-10-12T17:13:45.717Z</t>
+  </si>
+  <si>
+    <t>Contact us to arrange an interview</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board/EdwardShellard</t>
+  </si>
+  <si>
     <t>newsroom/media-relations-contacts.report.json</t>
   </si>
   <si>
@@ -286,6 +547,39 @@
     <t>https://www.highmark.com/newsroom/media-relations-contacts?zg=false</t>
   </si>
   <si>
+    <t>newsroom/news-alert.report.json</t>
+  </si>
+  <si>
+    <t>newsroom/news-alert</t>
+  </si>
+  <si>
+    <t>news-alert</t>
+  </si>
+  <si>
+    <t>2026-10-06T08:21:04.109Z</t>
+  </si>
+  <si>
+    <t>News Alert</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/newsroom/news-alert</t>
+  </si>
+  <si>
+    <t>newsroom/press-releases.report.json</t>
+  </si>
+  <si>
+    <t>newsroom/press-releases</t>
+  </si>
+  <si>
+    <t>press-releases</t>
+  </si>
+  <si>
+    <t>2026-10-06T11:37:38.711Z</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/newsroom/press-releases</t>
+  </si>
+  <si>
     <t>newsroom/weekly-capitol-hill-report.report.json</t>
   </si>
   <si>
@@ -421,6 +715,30 @@
     <t>https://www.highmark.com/resources/spending-accounts</t>
   </si>
   <si>
+    <t>shop/index.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-withimg","cards"]</t>
+  </si>
+  <si>
+    <t>2026-10-07T06:16:39.142Z; zip=15222; county=ALLEGHENY; region=Western PA</t>
+  </si>
+  <si>
+    <t>shop/index</t>
+  </si>
+  <si>
+    <t>shop-home</t>
+  </si>
+  <si>
+    <t>2026-10-07T07:01:01.218Z</t>
+  </si>
+  <si>
+    <t>Shop | Home</t>
+  </si>
+  <si>
+    <t>http://localhost:8765/shop/index.html</t>
+  </si>
+  <si>
     <t>western-pennsylvania/chip.report.json</t>
   </si>
   <si>
@@ -523,9 +841,6 @@
     <t>2026-09-30T20:31:22.630Z</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>https://www.highmark.com/about/our-story/leadership-team-board?zg=false</t>
   </si>
   <si>
@@ -913,6 +1228,69 @@
     <t>https://www.highmark.com/resources/spending-accounts/health-saving-account-hsa</t>
   </si>
   <si>
+    <t>shop/fragments/shopx-header-blue-edge-balance.report.json</t>
+  </si>
+  <si>
+    <t>2026-10-08T09:14:47.835Z; zip=15222; county=ALLEGHENY; region=</t>
+  </si>
+  <si>
+    <t>shop/fragments/shopx-header-blue-edge-balance</t>
+  </si>
+  <si>
+    <t>shop-header-fragment</t>
+  </si>
+  <si>
+    <t>2026-10-08T09:24:35.056Z</t>
+  </si>
+  <si>
+    <t>Shop Blue Edge Balance Plans</t>
+  </si>
+  <si>
+    <t>http://localhost:8765/shop/about-you/build-your-family/blue-edge-balance-enrollment.html?fragment=header</t>
+  </si>
+  <si>
+    <t>shop/fragments/shopx-header-dental.report.json</t>
+  </si>
+  <si>
+    <t>2026-10-08T09:14:36.389Z; zip=15222; county=ALLEGHENY; region=</t>
+  </si>
+  <si>
+    <t>shop/fragments/shopx-header-dental</t>
+  </si>
+  <si>
+    <t>2026-10-08T09:24:31.425Z</t>
+  </si>
+  <si>
+    <t>Shop Dental Plans</t>
+  </si>
+  <si>
+    <t>http://localhost:8765/shop/about-you/build-your-family/dental-enrollment.html?fragment=header</t>
+  </si>
+  <si>
+    <t>shop/info-pages/legal-policies.report.json</t>
+  </si>
+  <si>
+    <t>2026-10-08T09:19:53.553206Z; live page body is empty, so this is the page already migrated to DA (/shop/info-pages/legal-policies), re-imported for the ShopX layout</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>shop/info-pages/legal-policies</t>
+  </si>
+  <si>
+    <t>shop-page</t>
+  </si>
+  <si>
+    <t>2026-10-08T09:24:12.406Z</t>
+  </si>
+  <si>
+    <t>Shop | Legal Policies</t>
+  </si>
+  <si>
+    <t>http://localhost:8765/shop/info-pages/legal-policies.html</t>
+  </si>
+  <si>
     <t>western-pennsylvania/chip/chip-eligibility-and-costs.report.json</t>
   </si>
   <si>
@@ -1000,6 +1378,231 @@
     <t>https://www.highmark.com/western-pennsylvania/chip/what-is-chip?zg=false</t>
   </si>
   <si>
+    <t>about/our-story/leadership-team-board/anthony-benevento.report.json</t>
+  </si>
+  <si>
+    <t>["columns-minimal-dark"]</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/anthony-benevento</t>
+  </si>
+  <si>
+    <t>leadership-bio</t>
+  </si>
+  <si>
+    <t>2026-10-12T17:12:09.343Z</t>
+  </si>
+  <si>
+    <t>Anthony N. Benevento</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board/anthony-benevento</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/dan-tropeano.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/dan-tropeano</t>
+  </si>
+  <si>
+    <t>2026-10-12T17:12:34.656Z</t>
+  </si>
+  <si>
+    <t>Dan Tropeano</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board/dan-tropeano</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/david-holmberg.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/david-holmberg</t>
+  </si>
+  <si>
+    <t>2026-10-12T17:12:39.772Z</t>
+  </si>
+  <si>
+    <t>David L. Holmberg</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board/david-holmberg</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/edwardshellard.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/edwardshellard</t>
+  </si>
+  <si>
+    <t>2026-10-12T17:12:03.273Z</t>
+  </si>
+  <si>
+    <t>Edward Shellard</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/gustavo-giraldo.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/gustavo-giraldo</t>
+  </si>
+  <si>
+    <t>2026-10-13T12:06:07.816Z</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board/gustavo-giraldo</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/jaysheehy.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/jaysheehy</t>
+  </si>
+  <si>
+    <t>2026-10-13T12:05:55.616Z</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board/JaySheehy</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/jessicacox.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/jessicacox</t>
+  </si>
+  <si>
+    <t>2026-10-13T13:45:29.170Z</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board/JessicaCox</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/joehaddock.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/joehaddock</t>
+  </si>
+  <si>
+    <t>2026-10-12T17:12:25.748Z</t>
+  </si>
+  <si>
+    <t>Joe Haddock</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board/JoeHaddock</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/joy-matoney.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/joy-matoney</t>
+  </si>
+  <si>
+    <t>2026-10-12T17:11:46.384Z</t>
+  </si>
+  <si>
+    <t>Joy Matoney</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board/joy-matoney</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/kate-musler.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/kate-musler</t>
+  </si>
+  <si>
+    <t>2026-10-13T12:06:13.055Z</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board/kate-musler-</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/mark-lawrence.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/mark-lawrence</t>
+  </si>
+  <si>
+    <t>2026-10-12T17:11:41.380Z</t>
+  </si>
+  <si>
+    <t>Mark Lawrence</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board/mark-lawrence</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/matthew-rhenish.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/matthew-rhenish</t>
+  </si>
+  <si>
+    <t>2026-10-12T17:11:57.133Z</t>
+  </si>
+  <si>
+    <t>Matthew J. Rhenish</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board/matthew-rhenish</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/sarah-marche.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/sarah-marche</t>
+  </si>
+  <si>
+    <t>2026-10-12T17:12:30.408Z</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board/sarah-marche</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/thomas-fitzpatrick.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/thomas-fitzpatrick</t>
+  </si>
+  <si>
+    <t>2026-10-12T17:12:19.485Z</t>
+  </si>
+  <si>
+    <t>Thomas Fitzpatrick</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board/thomas-fitzpatrick</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/timothy-vessel.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/timothy-vessel</t>
+  </si>
+  <si>
+    <t>2026-10-13T13:44:36.218Z</t>
+  </si>
+  <si>
+    <t>Timothy Vessel</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board/Timothy-Vessel</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/victorfields.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board/victorfields</t>
+  </si>
+  <si>
+    <t>2026-10-13T12:06:02.363Z</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board/VictorFields</t>
+  </si>
+  <si>
     <t>resources/answers/articles/spending-accounts.report.json</t>
   </si>
   <si>
@@ -1367,6 +1970,66 @@
   </si>
   <si>
     <t>https://www.highmark.com/resources/mental-health-services/eating-disorders/help-someone-with-eating-disorder</t>
+  </si>
+  <si>
+    <t>shop/about-you/build-your-family/blue-edge-balance-enrollment.report.json</t>
+  </si>
+  <si>
+    <t>["enrollment-form"]</t>
+  </si>
+  <si>
+    <t>enrollment</t>
+  </si>
+  <si>
+    <t>shop/about-you/build-your-family/blue-edge-balance-enrollment</t>
+  </si>
+  <si>
+    <t>2026-10-08T09:24:26.632Z</t>
+  </si>
+  <si>
+    <t>Shop | Blue Edge Balance Enrollment</t>
+  </si>
+  <si>
+    <t>http://localhost:8765/shop/about-you/build-your-family/blue-edge-balance-enrollment.html</t>
+  </si>
+  <si>
+    <t>shop/about-you/build-your-family/dental-enrollment.report.json</t>
+  </si>
+  <si>
+    <t>shop/about-you/build-your-family/dental-enrollment</t>
+  </si>
+  <si>
+    <t>2026-10-08T09:24:22.193Z</t>
+  </si>
+  <si>
+    <t>Shop | Dental Enrollment</t>
+  </si>
+  <si>
+    <t>http://localhost:8765/shop/about-you/build-your-family/dental-enrollment.html</t>
+  </si>
+  <si>
+    <t>shop/about-you/qualifying-life-events/landing.report.json</t>
+  </si>
+  <si>
+    <t>["flip-cards"]</t>
+  </si>
+  <si>
+    <t>2026-10-08T09:14:24.753Z; zip=15222; county=ALLEGHENY; region=Western PA</t>
+  </si>
+  <si>
+    <t>qle</t>
+  </si>
+  <si>
+    <t>shop/about-you/qualifying-life-events/landing</t>
+  </si>
+  <si>
+    <t>2026-10-08T09:24:17.760Z</t>
+  </si>
+  <si>
+    <t>Shop | Special Enrollment Qualification</t>
+  </si>
+  <si>
+    <t>http://localhost:8765/shop/about-you/qualifying-life-events/landing.html</t>
   </si>
 </sst>
 </file>
@@ -1755,16 +2418,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="8" width="50" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="50" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="11" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1789,918 +2455,1242 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="I7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s">
         <v>34</v>
       </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" t="s">
-        <v>54</v>
-      </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="I9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" t="s">
+        <v>62</v>
+      </c>
+      <c r="K9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
         <v>81</v>
       </c>
       <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
         <v>82</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J13" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="F14" t="s">
         <v>88</v>
       </c>
       <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" t="s">
         <v>89</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="F15" t="s">
         <v>94</v>
       </c>
       <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" t="s">
         <v>95</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
         <v>100</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>100</v>
+      </c>
+      <c r="I16" t="s">
         <v>101</v>
       </c>
-      <c r="G16" t="s">
+      <c r="J16" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" t="s">
         <v>102</v>
       </c>
-      <c r="H16" t="s">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>104</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
         <v>105</v>
       </c>
-      <c r="C17" t="s">
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" t="s">
         <v>106</v>
       </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="I17" t="s">
         <v>107</v>
       </c>
-      <c r="F17" t="s">
+      <c r="J17" t="s">
         <v>108</v>
       </c>
-      <c r="G17" t="s">
+      <c r="K17" t="s">
         <v>109</v>
       </c>
-      <c r="H17" t="s">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>111</v>
       </c>
-      <c r="B18" t="s">
-        <v>98</v>
-      </c>
       <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
         <v>112</v>
       </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" t="s">
-        <v>100</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
         <v>113</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>114</v>
       </c>
-      <c r="H18" t="s">
+      <c r="J18" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
         <v>118</v>
       </c>
-      <c r="D19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" t="s">
+        <v>106</v>
+      </c>
+      <c r="I19" t="s">
         <v>119</v>
       </c>
-      <c r="F19" t="s">
+      <c r="J19" t="s">
         <v>120</v>
       </c>
-      <c r="G19" t="s">
+      <c r="K19" t="s">
         <v>121</v>
       </c>
-      <c r="H19" t="s">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>123</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
         <v>124</v>
       </c>
-      <c r="C20" t="s">
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s">
         <v>125</v>
       </c>
-      <c r="D20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" t="s">
-        <v>37</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="J20" t="s">
         <v>126</v>
       </c>
-      <c r="G20" t="s">
+      <c r="K20" t="s">
         <v>127</v>
       </c>
-      <c r="H20" t="s">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>129</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
         <v>130</v>
       </c>
-      <c r="C21" t="s">
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" t="s">
         <v>131</v>
       </c>
-      <c r="D21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="I21" t="s">
         <v>132</v>
       </c>
-      <c r="F21" t="s">
+      <c r="J21" t="s">
         <v>133</v>
       </c>
-      <c r="G21" t="s">
+      <c r="K21" t="s">
         <v>134</v>
       </c>
-      <c r="H21" t="s">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
         <v>136</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s">
         <v>137</v>
       </c>
-      <c r="C22" t="s">
+      <c r="G22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" t="s">
+        <v>131</v>
+      </c>
+      <c r="I22" t="s">
         <v>138</v>
       </c>
-      <c r="D22" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="J22" t="s">
         <v>139</v>
       </c>
-      <c r="F22" t="s">
+      <c r="K22" t="s">
         <v>140</v>
       </c>
-      <c r="G22" t="s">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>141</v>
       </c>
-      <c r="H22" t="s">
+      <c r="B23" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" t="s">
         <v>143</v>
       </c>
-      <c r="B23" t="s">
+      <c r="G23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" t="s">
+        <v>131</v>
+      </c>
+      <c r="I23" t="s">
         <v>144</v>
       </c>
-      <c r="C23" t="s">
+      <c r="J23" t="s">
         <v>145</v>
       </c>
-      <c r="D23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="K23" t="s">
         <v>146</v>
       </c>
-      <c r="F23" t="s">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>147</v>
       </c>
-      <c r="G23" t="s">
+      <c r="B24" t="s">
         <v>148</v>
       </c>
-      <c r="H23" t="s">
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" t="s">
+        <v>131</v>
+      </c>
+      <c r="I24" t="s">
         <v>150</v>
       </c>
-      <c r="B24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="J24" t="s">
         <v>151</v>
       </c>
-      <c r="D24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="K24" t="s">
         <v>152</v>
       </c>
-      <c r="G24" t="s">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>153</v>
       </c>
-      <c r="H24" t="s">
+      <c r="B25" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" t="s">
         <v>155</v>
       </c>
-      <c r="B25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" t="s">
+        <v>131</v>
+      </c>
+      <c r="I25" t="s">
         <v>156</v>
       </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="J25" t="s">
         <v>157</v>
       </c>
-      <c r="G25" t="s">
+      <c r="K25" t="s">
         <v>158</v>
       </c>
-      <c r="H25" t="s">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
         <v>160</v>
       </c>
-      <c r="B26" t="s">
-        <v>42</v>
-      </c>
       <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
         <v>161</v>
       </c>
-      <c r="D26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" t="s">
         <v>162</v>
       </c>
-      <c r="G26" t="s">
+      <c r="I26" t="s">
         <v>163</v>
       </c>
-      <c r="H26" t="s">
+      <c r="J26" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K26" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
         <v>167</v>
       </c>
-      <c r="D27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="G27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" t="s">
         <v>168</v>
       </c>
-      <c r="F27" t="s">
+      <c r="J27" t="s">
         <v>169</v>
       </c>
-      <c r="G27" t="s">
+      <c r="K27" t="s">
         <v>170</v>
       </c>
-      <c r="H27" t="s">
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>172</v>
       </c>
-      <c r="B28" t="s">
-        <v>42</v>
-      </c>
       <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s">
         <v>173</v>
       </c>
-      <c r="D28" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" t="s">
         <v>174</v>
       </c>
-      <c r="G28" t="s">
+      <c r="I28" t="s">
         <v>175</v>
       </c>
-      <c r="H28" t="s">
+      <c r="J28" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K28" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>178</v>
+        <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="F29" t="s">
         <v>179</v>
       </c>
       <c r="G29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" t="s">
         <v>180</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J29" t="s">
+        <v>182</v>
+      </c>
+      <c r="K29" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B30" t="s">
-        <v>183</v>
+        <v>111</v>
       </c>
       <c r="C30" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" t="s">
         <v>185</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" t="s">
         <v>186</v>
       </c>
-      <c r="G30" t="s">
+      <c r="I30" t="s">
         <v>187</v>
       </c>
-      <c r="H30" t="s">
+      <c r="J30" t="s">
+        <v>13</v>
+      </c>
+      <c r="K30" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>189</v>
       </c>
       <c r="B31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" t="s">
         <v>190</v>
       </c>
-      <c r="C31" t="s">
+      <c r="G31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" t="s">
         <v>191</v>
       </c>
-      <c r="D31" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="I31" t="s">
         <v>192</v>
       </c>
-      <c r="F31" t="s">
+      <c r="J31" t="s">
         <v>193</v>
       </c>
-      <c r="G31" t="s">
+      <c r="K31" t="s">
         <v>194</v>
       </c>
-      <c r="H31" t="s">
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>196</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" t="s">
         <v>197</v>
       </c>
-      <c r="C32" t="s">
+      <c r="G32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" t="s">
         <v>198</v>
       </c>
-      <c r="D32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="I32" t="s">
         <v>199</v>
       </c>
-      <c r="F32" t="s">
+      <c r="J32" t="s">
         <v>200</v>
       </c>
-      <c r="G32" t="s">
+      <c r="K32" t="s">
         <v>201</v>
       </c>
-      <c r="H32" t="s">
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>203</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" t="s">
         <v>204</v>
       </c>
-      <c r="C33" t="s">
+      <c r="G33" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" t="s">
         <v>205</v>
       </c>
-      <c r="D33" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" t="s">
-        <v>192</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="I33" t="s">
         <v>206</v>
       </c>
-      <c r="G33" t="s">
+      <c r="J33" t="s">
         <v>207</v>
       </c>
-      <c r="H33" t="s">
+      <c r="K33" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>209</v>
       </c>
       <c r="B34" t="s">
+        <v>196</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" t="s">
         <v>210</v>
       </c>
-      <c r="C34" t="s">
+      <c r="G34" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" t="s">
+        <v>198</v>
+      </c>
+      <c r="I34" t="s">
         <v>211</v>
       </c>
-      <c r="D34" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="J34" t="s">
         <v>212</v>
       </c>
-      <c r="F34" t="s">
+      <c r="K34" t="s">
         <v>213</v>
       </c>
-      <c r="G34" t="s">
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>214</v>
       </c>
-      <c r="H34" t="s">
+      <c r="B35" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" t="s">
         <v>216</v>
       </c>
-      <c r="B35" t="s">
-        <v>42</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="G35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" t="s">
         <v>217</v>
       </c>
-      <c r="D35" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="I35" t="s">
         <v>218</v>
       </c>
-      <c r="F35" t="s">
+      <c r="J35" t="s">
         <v>219</v>
       </c>
-      <c r="G35" t="s">
+      <c r="K35" t="s">
         <v>220</v>
       </c>
-      <c r="H35" t="s">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
         <v>222</v>
       </c>
-      <c r="B36" t="s">
-        <v>42</v>
-      </c>
       <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" t="s">
         <v>223</v>
       </c>
-      <c r="D36" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" t="s">
-        <v>218</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
+        <v>82</v>
+      </c>
+      <c r="I36" t="s">
         <v>224</v>
       </c>
-      <c r="G36" t="s">
+      <c r="J36" t="s">
         <v>225</v>
       </c>
-      <c r="H36" t="s">
+      <c r="K36" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>227</v>
       </c>
@@ -2708,1066 +3698,2800 @@
         <v>228</v>
       </c>
       <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" t="s">
         <v>229</v>
       </c>
-      <c r="D37" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" t="s">
-        <v>218</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" t="s">
         <v>230</v>
       </c>
-      <c r="G37" t="s">
+      <c r="I37" t="s">
         <v>231</v>
       </c>
-      <c r="H37" t="s">
+      <c r="J37" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K37" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B38" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C38" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="F38" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G38" t="s">
-        <v>237</v>
+        <v>15</v>
       </c>
       <c r="H38" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I38" t="s">
+        <v>239</v>
+      </c>
+      <c r="J38" t="s">
+        <v>240</v>
+      </c>
+      <c r="K38" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B39" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C39" t="s">
-        <v>241</v>
+        <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="F39" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G39" t="s">
-        <v>243</v>
+        <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+      <c r="I39" t="s">
+        <v>246</v>
+      </c>
+      <c r="J39" t="s">
+        <v>247</v>
+      </c>
+      <c r="K39" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B40" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C40" t="s">
-        <v>246</v>
+        <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="F40" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="G40" t="s">
-        <v>248</v>
+        <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+      <c r="I40" t="s">
+        <v>253</v>
+      </c>
+      <c r="J40" t="s">
+        <v>254</v>
+      </c>
+      <c r="K40" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B41" t="s">
-        <v>240</v>
+        <v>104</v>
       </c>
       <c r="C41" t="s">
-        <v>251</v>
+        <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="F41" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="G41" t="s">
-        <v>253</v>
+        <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="I41" t="s">
+        <v>258</v>
+      </c>
+      <c r="J41" t="s">
+        <v>259</v>
+      </c>
+      <c r="K41" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B42" t="s">
-        <v>256</v>
+        <v>104</v>
       </c>
       <c r="C42" t="s">
-        <v>257</v>
+        <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="F42" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G42" t="s">
-        <v>259</v>
+        <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="I42" t="s">
+        <v>263</v>
+      </c>
+      <c r="J42" t="s">
+        <v>264</v>
+      </c>
+      <c r="K42" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B43" t="s">
-        <v>262</v>
+        <v>104</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="F43" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G43" t="s">
-        <v>265</v>
+        <v>15</v>
       </c>
       <c r="H43" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="I43" t="s">
+        <v>268</v>
+      </c>
+      <c r="J43" t="s">
+        <v>269</v>
+      </c>
+      <c r="K43" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B44" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="C44" t="s">
-        <v>268</v>
+        <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="F44" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G44" t="s">
-        <v>270</v>
+        <v>15</v>
       </c>
       <c r="H44" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+      <c r="I44" t="s">
+        <v>275</v>
+      </c>
+      <c r="J44" t="s">
+        <v>13</v>
+      </c>
+      <c r="K44" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="C45" t="s">
-        <v>273</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>274</v>
+        <v>13</v>
       </c>
       <c r="F45" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G45" t="s">
-        <v>276</v>
+        <v>15</v>
       </c>
       <c r="H45" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="I45" t="s">
+        <v>279</v>
+      </c>
+      <c r="J45" t="s">
+        <v>280</v>
+      </c>
+      <c r="K45" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B46" t="s">
-        <v>279</v>
+        <v>104</v>
       </c>
       <c r="C46" t="s">
-        <v>280</v>
+        <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="F46" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G46" t="s">
-        <v>282</v>
+        <v>15</v>
       </c>
       <c r="H46" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="I46" t="s">
+        <v>284</v>
+      </c>
+      <c r="J46" t="s">
+        <v>285</v>
+      </c>
+      <c r="K46" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B47" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C47" t="s">
-        <v>286</v>
+        <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="F47" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G47" t="s">
-        <v>288</v>
+        <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+      <c r="I47" t="s">
+        <v>291</v>
+      </c>
+      <c r="J47" t="s">
+        <v>292</v>
+      </c>
+      <c r="K47" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B48" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="C48" t="s">
-        <v>291</v>
+        <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E48" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="F48" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="G48" t="s">
-        <v>293</v>
+        <v>15</v>
       </c>
       <c r="H48" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+      <c r="I48" t="s">
+        <v>298</v>
+      </c>
+      <c r="J48" t="s">
+        <v>299</v>
+      </c>
+      <c r="K48" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B49" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="C49" t="s">
-        <v>296</v>
+        <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E49" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="F49" t="s">
+        <v>303</v>
+      </c>
+      <c r="G49" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" t="s">
+        <v>304</v>
+      </c>
+      <c r="I49" t="s">
+        <v>305</v>
+      </c>
+      <c r="J49" t="s">
+        <v>306</v>
+      </c>
+      <c r="K49" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>308</v>
+      </c>
+      <c r="B50" t="s">
+        <v>309</v>
+      </c>
+      <c r="C50" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" t="s">
+        <v>310</v>
+      </c>
+      <c r="G50" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" t="s">
         <v>297</v>
       </c>
-      <c r="G49" t="s">
-        <v>298</v>
-      </c>
-      <c r="H49" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>300</v>
-      </c>
-      <c r="B50" t="s">
-        <v>301</v>
-      </c>
-      <c r="C50" t="s">
-        <v>302</v>
-      </c>
-      <c r="D50" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" t="s">
-        <v>303</v>
-      </c>
-      <c r="F50" t="s">
-        <v>304</v>
-      </c>
-      <c r="G50" t="s">
-        <v>305</v>
-      </c>
-      <c r="H50" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I50" t="s">
+        <v>311</v>
+      </c>
+      <c r="J50" t="s">
+        <v>312</v>
+      </c>
+      <c r="K50" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B51" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C51" t="s">
-        <v>309</v>
+        <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E51" t="s">
-        <v>303</v>
+        <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="G51" t="s">
-        <v>311</v>
+        <v>15</v>
       </c>
       <c r="H51" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+      <c r="I51" t="s">
+        <v>318</v>
+      </c>
+      <c r="J51" t="s">
+        <v>319</v>
+      </c>
+      <c r="K51" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B52" t="s">
-        <v>308</v>
+        <v>104</v>
       </c>
       <c r="C52" t="s">
-        <v>314</v>
+        <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>303</v>
+        <v>13</v>
       </c>
       <c r="F52" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="G52" t="s">
-        <v>316</v>
+        <v>15</v>
       </c>
       <c r="H52" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+      <c r="I52" t="s">
+        <v>324</v>
+      </c>
+      <c r="J52" t="s">
+        <v>325</v>
+      </c>
+      <c r="K52" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="B53" t="s">
-        <v>308</v>
+        <v>104</v>
       </c>
       <c r="C53" t="s">
-        <v>319</v>
+        <v>13</v>
       </c>
       <c r="D53" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E53" t="s">
-        <v>303</v>
+        <v>13</v>
       </c>
       <c r="F53" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="G53" t="s">
-        <v>321</v>
+        <v>15</v>
       </c>
       <c r="H53" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+      <c r="I53" t="s">
+        <v>329</v>
+      </c>
+      <c r="J53" t="s">
+        <v>330</v>
+      </c>
+      <c r="K53" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>332</v>
+      </c>
+      <c r="B54" t="s">
+        <v>333</v>
+      </c>
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" t="s">
+        <v>334</v>
+      </c>
+      <c r="G54" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" t="s">
         <v>323</v>
       </c>
-      <c r="B54" t="s">
-        <v>324</v>
-      </c>
-      <c r="C54" t="s">
-        <v>325</v>
-      </c>
-      <c r="D54" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" t="s">
-        <v>303</v>
-      </c>
-      <c r="F54" t="s">
-        <v>326</v>
-      </c>
-      <c r="G54" t="s">
-        <v>327</v>
-      </c>
-      <c r="H54" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I54" t="s">
+        <v>335</v>
+      </c>
+      <c r="J54" t="s">
+        <v>336</v>
+      </c>
+      <c r="K54" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B55" t="s">
-        <v>42</v>
+        <v>339</v>
       </c>
       <c r="C55" t="s">
-        <v>330</v>
+        <v>13</v>
       </c>
       <c r="D55" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E55" t="s">
-        <v>331</v>
+        <v>13</v>
       </c>
       <c r="F55" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="G55" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" t="s">
+        <v>217</v>
+      </c>
+      <c r="I55" t="s">
+        <v>341</v>
+      </c>
+      <c r="J55" t="s">
+        <v>342</v>
+      </c>
+      <c r="K55" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>344</v>
+      </c>
+      <c r="B56" t="s">
+        <v>345</v>
+      </c>
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" t="s">
+        <v>346</v>
+      </c>
+      <c r="G56" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" t="s">
+        <v>230</v>
+      </c>
+      <c r="I56" t="s">
+        <v>347</v>
+      </c>
+      <c r="J56" t="s">
+        <v>348</v>
+      </c>
+      <c r="K56" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>350</v>
+      </c>
+      <c r="B57" t="s">
+        <v>345</v>
+      </c>
+      <c r="C57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" t="s">
+        <v>351</v>
+      </c>
+      <c r="G57" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" t="s">
+        <v>230</v>
+      </c>
+      <c r="I57" t="s">
+        <v>352</v>
+      </c>
+      <c r="J57" t="s">
+        <v>353</v>
+      </c>
+      <c r="K57" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>355</v>
+      </c>
+      <c r="B58" t="s">
+        <v>345</v>
+      </c>
+      <c r="C58" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" t="s">
+        <v>356</v>
+      </c>
+      <c r="G58" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" t="s">
+        <v>230</v>
+      </c>
+      <c r="I58" t="s">
+        <v>357</v>
+      </c>
+      <c r="J58" t="s">
+        <v>358</v>
+      </c>
+      <c r="K58" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>360</v>
+      </c>
+      <c r="B59" t="s">
+        <v>361</v>
+      </c>
+      <c r="C59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" t="s">
+        <v>362</v>
+      </c>
+      <c r="G59" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" t="s">
+        <v>230</v>
+      </c>
+      <c r="I59" t="s">
+        <v>363</v>
+      </c>
+      <c r="J59" t="s">
+        <v>364</v>
+      </c>
+      <c r="K59" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>366</v>
+      </c>
+      <c r="B60" t="s">
+        <v>367</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" t="s">
+        <v>368</v>
+      </c>
+      <c r="G60" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" t="s">
+        <v>230</v>
+      </c>
+      <c r="I60" t="s">
+        <v>369</v>
+      </c>
+      <c r="J60" t="s">
+        <v>370</v>
+      </c>
+      <c r="K60" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>372</v>
+      </c>
+      <c r="B61" t="s">
+        <v>345</v>
+      </c>
+      <c r="C61" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" t="s">
+        <v>373</v>
+      </c>
+      <c r="G61" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" t="s">
+        <v>230</v>
+      </c>
+      <c r="I61" t="s">
+        <v>374</v>
+      </c>
+      <c r="J61" t="s">
+        <v>375</v>
+      </c>
+      <c r="K61" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>377</v>
+      </c>
+      <c r="B62" t="s">
+        <v>104</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" t="s">
+        <v>378</v>
+      </c>
+      <c r="G62" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" t="s">
+        <v>379</v>
+      </c>
+      <c r="I62" t="s">
+        <v>380</v>
+      </c>
+      <c r="J62" t="s">
+        <v>381</v>
+      </c>
+      <c r="K62" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>383</v>
+      </c>
+      <c r="B63" t="s">
+        <v>384</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" t="s">
+        <v>385</v>
+      </c>
+      <c r="G63" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" t="s">
+        <v>217</v>
+      </c>
+      <c r="I63" t="s">
+        <v>386</v>
+      </c>
+      <c r="J63" t="s">
+        <v>387</v>
+      </c>
+      <c r="K63" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>389</v>
+      </c>
+      <c r="B64" t="s">
+        <v>390</v>
+      </c>
+      <c r="C64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" t="s">
+        <v>391</v>
+      </c>
+      <c r="G64" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" t="s">
+        <v>217</v>
+      </c>
+      <c r="I64" t="s">
+        <v>392</v>
+      </c>
+      <c r="J64" t="s">
+        <v>393</v>
+      </c>
+      <c r="K64" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>395</v>
+      </c>
+      <c r="B65" t="s">
+        <v>384</v>
+      </c>
+      <c r="C65" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" t="s">
+        <v>396</v>
+      </c>
+      <c r="G65" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" t="s">
+        <v>217</v>
+      </c>
+      <c r="I65" t="s">
+        <v>397</v>
+      </c>
+      <c r="J65" t="s">
+        <v>398</v>
+      </c>
+      <c r="K65" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>400</v>
+      </c>
+      <c r="B66" t="s">
+        <v>390</v>
+      </c>
+      <c r="C66" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" t="s">
+        <v>401</v>
+      </c>
+      <c r="G66" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" t="s">
+        <v>217</v>
+      </c>
+      <c r="I66" t="s">
+        <v>402</v>
+      </c>
+      <c r="J66" t="s">
+        <v>403</v>
+      </c>
+      <c r="K66" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>405</v>
+      </c>
+      <c r="B67" t="s">
+        <v>34</v>
+      </c>
+      <c r="C67" t="s">
+        <v>406</v>
+      </c>
+      <c r="D67" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" t="s">
+        <v>407</v>
+      </c>
+      <c r="G67" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" t="s">
+        <v>408</v>
+      </c>
+      <c r="I67" t="s">
+        <v>409</v>
+      </c>
+      <c r="J67" t="s">
+        <v>410</v>
+      </c>
+      <c r="K67" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>412</v>
+      </c>
+      <c r="B68" t="s">
+        <v>34</v>
+      </c>
+      <c r="C68" t="s">
+        <v>413</v>
+      </c>
+      <c r="D68" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" t="s">
+        <v>414</v>
+      </c>
+      <c r="G68" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" t="s">
+        <v>408</v>
+      </c>
+      <c r="I68" t="s">
+        <v>415</v>
+      </c>
+      <c r="J68" t="s">
+        <v>416</v>
+      </c>
+      <c r="K68" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>418</v>
+      </c>
+      <c r="B69" t="s">
+        <v>34</v>
+      </c>
+      <c r="C69" t="s">
+        <v>419</v>
+      </c>
+      <c r="D69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" t="s">
+        <v>420</v>
+      </c>
+      <c r="F69" t="s">
+        <v>421</v>
+      </c>
+      <c r="G69" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" t="s">
+        <v>422</v>
+      </c>
+      <c r="I69" t="s">
+        <v>423</v>
+      </c>
+      <c r="J69" t="s">
+        <v>424</v>
+      </c>
+      <c r="K69" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>426</v>
+      </c>
+      <c r="B70" t="s">
+        <v>427</v>
+      </c>
+      <c r="C70" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" t="s">
+        <v>428</v>
+      </c>
+      <c r="G70" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" t="s">
+        <v>429</v>
+      </c>
+      <c r="I70" t="s">
+        <v>430</v>
+      </c>
+      <c r="J70" t="s">
+        <v>431</v>
+      </c>
+      <c r="K70" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>433</v>
+      </c>
+      <c r="B71" t="s">
+        <v>434</v>
+      </c>
+      <c r="C71" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" t="s">
+        <v>435</v>
+      </c>
+      <c r="G71" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" t="s">
+        <v>429</v>
+      </c>
+      <c r="I71" t="s">
+        <v>436</v>
+      </c>
+      <c r="J71" t="s">
+        <v>437</v>
+      </c>
+      <c r="K71" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>439</v>
+      </c>
+      <c r="B72" t="s">
+        <v>434</v>
+      </c>
+      <c r="C72" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" t="s">
+        <v>440</v>
+      </c>
+      <c r="G72" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" t="s">
+        <v>429</v>
+      </c>
+      <c r="I72" t="s">
+        <v>441</v>
+      </c>
+      <c r="J72" t="s">
+        <v>442</v>
+      </c>
+      <c r="K72" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>444</v>
+      </c>
+      <c r="B73" t="s">
+        <v>434</v>
+      </c>
+      <c r="C73" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" t="s">
+        <v>445</v>
+      </c>
+      <c r="G73" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" t="s">
+        <v>429</v>
+      </c>
+      <c r="I73" t="s">
+        <v>446</v>
+      </c>
+      <c r="J73" t="s">
+        <v>447</v>
+      </c>
+      <c r="K73" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>449</v>
+      </c>
+      <c r="B74" t="s">
+        <v>450</v>
+      </c>
+      <c r="C74" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" t="s">
+        <v>451</v>
+      </c>
+      <c r="G74" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" t="s">
+        <v>429</v>
+      </c>
+      <c r="I74" t="s">
+        <v>452</v>
+      </c>
+      <c r="J74" t="s">
+        <v>453</v>
+      </c>
+      <c r="K74" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>455</v>
+      </c>
+      <c r="B75" t="s">
+        <v>456</v>
+      </c>
+      <c r="C75" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" t="s">
+        <v>457</v>
+      </c>
+      <c r="G75" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" t="s">
+        <v>458</v>
+      </c>
+      <c r="I75" t="s">
+        <v>459</v>
+      </c>
+      <c r="J75" t="s">
+        <v>460</v>
+      </c>
+      <c r="K75" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>462</v>
+      </c>
+      <c r="B76" t="s">
+        <v>456</v>
+      </c>
+      <c r="C76" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" t="s">
+        <v>463</v>
+      </c>
+      <c r="G76" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" t="s">
+        <v>458</v>
+      </c>
+      <c r="I76" t="s">
+        <v>464</v>
+      </c>
+      <c r="J76" t="s">
+        <v>465</v>
+      </c>
+      <c r="K76" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>467</v>
+      </c>
+      <c r="B77" t="s">
+        <v>456</v>
+      </c>
+      <c r="C77" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" t="s">
+        <v>468</v>
+      </c>
+      <c r="G77" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" t="s">
+        <v>458</v>
+      </c>
+      <c r="I77" t="s">
+        <v>469</v>
+      </c>
+      <c r="J77" t="s">
+        <v>470</v>
+      </c>
+      <c r="K77" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>472</v>
+      </c>
+      <c r="B78" t="s">
+        <v>456</v>
+      </c>
+      <c r="C78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" t="s">
+        <v>473</v>
+      </c>
+      <c r="G78" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" t="s">
+        <v>458</v>
+      </c>
+      <c r="I78" t="s">
+        <v>474</v>
+      </c>
+      <c r="J78" t="s">
+        <v>475</v>
+      </c>
+      <c r="K78" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>476</v>
+      </c>
+      <c r="B79" t="s">
+        <v>456</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" t="s">
+        <v>477</v>
+      </c>
+      <c r="G79" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" t="s">
+        <v>458</v>
+      </c>
+      <c r="I79" t="s">
+        <v>478</v>
+      </c>
+      <c r="J79" t="s">
+        <v>13</v>
+      </c>
+      <c r="K79" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>480</v>
+      </c>
+      <c r="B80" t="s">
+        <v>456</v>
+      </c>
+      <c r="C80" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" t="s">
+        <v>481</v>
+      </c>
+      <c r="G80" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" t="s">
+        <v>458</v>
+      </c>
+      <c r="I80" t="s">
+        <v>482</v>
+      </c>
+      <c r="J80" t="s">
+        <v>13</v>
+      </c>
+      <c r="K80" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>484</v>
+      </c>
+      <c r="B81" t="s">
+        <v>456</v>
+      </c>
+      <c r="C81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" t="s">
+        <v>485</v>
+      </c>
+      <c r="G81" t="s">
+        <v>15</v>
+      </c>
+      <c r="H81" t="s">
+        <v>458</v>
+      </c>
+      <c r="I81" t="s">
+        <v>486</v>
+      </c>
+      <c r="J81" t="s">
+        <v>13</v>
+      </c>
+      <c r="K81" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>488</v>
+      </c>
+      <c r="B82" t="s">
+        <v>456</v>
+      </c>
+      <c r="C82" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" t="s">
+        <v>489</v>
+      </c>
+      <c r="G82" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" t="s">
+        <v>458</v>
+      </c>
+      <c r="I82" t="s">
+        <v>490</v>
+      </c>
+      <c r="J82" t="s">
+        <v>491</v>
+      </c>
+      <c r="K82" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>493</v>
+      </c>
+      <c r="B83" t="s">
+        <v>456</v>
+      </c>
+      <c r="C83" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" t="s">
+        <v>494</v>
+      </c>
+      <c r="G83" t="s">
+        <v>15</v>
+      </c>
+      <c r="H83" t="s">
+        <v>458</v>
+      </c>
+      <c r="I83" t="s">
+        <v>495</v>
+      </c>
+      <c r="J83" t="s">
+        <v>496</v>
+      </c>
+      <c r="K83" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>498</v>
+      </c>
+      <c r="B84" t="s">
+        <v>456</v>
+      </c>
+      <c r="C84" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" t="s">
+        <v>499</v>
+      </c>
+      <c r="G84" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" t="s">
+        <v>458</v>
+      </c>
+      <c r="I84" t="s">
+        <v>500</v>
+      </c>
+      <c r="J84" t="s">
+        <v>13</v>
+      </c>
+      <c r="K84" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>502</v>
+      </c>
+      <c r="B85" t="s">
+        <v>456</v>
+      </c>
+      <c r="C85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" t="s">
+        <v>503</v>
+      </c>
+      <c r="G85" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" t="s">
+        <v>458</v>
+      </c>
+      <c r="I85" t="s">
+        <v>504</v>
+      </c>
+      <c r="J85" t="s">
+        <v>505</v>
+      </c>
+      <c r="K85" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>507</v>
+      </c>
+      <c r="B86" t="s">
+        <v>456</v>
+      </c>
+      <c r="C86" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" t="s">
+        <v>508</v>
+      </c>
+      <c r="G86" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" t="s">
+        <v>458</v>
+      </c>
+      <c r="I86" t="s">
+        <v>509</v>
+      </c>
+      <c r="J86" t="s">
+        <v>510</v>
+      </c>
+      <c r="K86" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>512</v>
+      </c>
+      <c r="B87" t="s">
+        <v>456</v>
+      </c>
+      <c r="C87" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" t="s">
+        <v>513</v>
+      </c>
+      <c r="G87" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" t="s">
+        <v>458</v>
+      </c>
+      <c r="I87" t="s">
+        <v>514</v>
+      </c>
+      <c r="J87" t="s">
+        <v>13</v>
+      </c>
+      <c r="K87" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>516</v>
+      </c>
+      <c r="B88" t="s">
+        <v>456</v>
+      </c>
+      <c r="C88" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" t="s">
+        <v>517</v>
+      </c>
+      <c r="G88" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" t="s">
+        <v>458</v>
+      </c>
+      <c r="I88" t="s">
+        <v>518</v>
+      </c>
+      <c r="J88" t="s">
+        <v>519</v>
+      </c>
+      <c r="K88" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>521</v>
+      </c>
+      <c r="B89" t="s">
+        <v>456</v>
+      </c>
+      <c r="C89" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" t="s">
+        <v>522</v>
+      </c>
+      <c r="G89" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" t="s">
+        <v>458</v>
+      </c>
+      <c r="I89" t="s">
+        <v>523</v>
+      </c>
+      <c r="J89" t="s">
+        <v>524</v>
+      </c>
+      <c r="K89" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>526</v>
+      </c>
+      <c r="B90" t="s">
+        <v>456</v>
+      </c>
+      <c r="C90" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" t="s">
+        <v>527</v>
+      </c>
+      <c r="G90" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" t="s">
+        <v>458</v>
+      </c>
+      <c r="I90" t="s">
+        <v>528</v>
+      </c>
+      <c r="J90" t="s">
+        <v>13</v>
+      </c>
+      <c r="K90" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>530</v>
+      </c>
+      <c r="B91" t="s">
+        <v>104</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" t="s">
+        <v>13</v>
+      </c>
+      <c r="F91" t="s">
+        <v>531</v>
+      </c>
+      <c r="G91" t="s">
+        <v>15</v>
+      </c>
+      <c r="H91" t="s">
+        <v>532</v>
+      </c>
+      <c r="I91" t="s">
+        <v>533</v>
+      </c>
+      <c r="J91" t="s">
+        <v>534</v>
+      </c>
+      <c r="K91" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>536</v>
+      </c>
+      <c r="B92" t="s">
+        <v>537</v>
+      </c>
+      <c r="C92" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" t="s">
+        <v>538</v>
+      </c>
+      <c r="G92" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" t="s">
+        <v>323</v>
+      </c>
+      <c r="I92" t="s">
+        <v>539</v>
+      </c>
+      <c r="J92" t="s">
+        <v>540</v>
+      </c>
+      <c r="K92" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>542</v>
+      </c>
+      <c r="B93" t="s">
+        <v>543</v>
+      </c>
+      <c r="C93" t="s">
+        <v>13</v>
+      </c>
+      <c r="D93" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93" t="s">
+        <v>544</v>
+      </c>
+      <c r="G93" t="s">
+        <v>15</v>
+      </c>
+      <c r="H93" t="s">
+        <v>545</v>
+      </c>
+      <c r="I93" t="s">
+        <v>546</v>
+      </c>
+      <c r="J93" t="s">
+        <v>547</v>
+      </c>
+      <c r="K93" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>549</v>
+      </c>
+      <c r="B94" t="s">
         <v>333</v>
       </c>
-      <c r="H55" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>335</v>
-      </c>
-      <c r="B56" t="s">
-        <v>336</v>
-      </c>
-      <c r="C56" t="s">
-        <v>337</v>
-      </c>
-      <c r="D56" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" t="s">
-        <v>218</v>
-      </c>
-      <c r="F56" t="s">
-        <v>338</v>
-      </c>
-      <c r="G56" t="s">
-        <v>339</v>
-      </c>
-      <c r="H56" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>341</v>
-      </c>
-      <c r="B57" t="s">
-        <v>342</v>
-      </c>
-      <c r="C57" t="s">
-        <v>343</v>
-      </c>
-      <c r="D57" t="s">
-        <v>11</v>
-      </c>
-      <c r="E57" t="s">
-        <v>344</v>
-      </c>
-      <c r="F57" t="s">
-        <v>345</v>
-      </c>
-      <c r="G57" t="s">
-        <v>346</v>
-      </c>
-      <c r="H57" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>348</v>
-      </c>
-      <c r="B58" t="s">
-        <v>228</v>
-      </c>
-      <c r="C58" t="s">
-        <v>349</v>
-      </c>
-      <c r="D58" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" t="s">
-        <v>218</v>
-      </c>
-      <c r="F58" t="s">
-        <v>350</v>
-      </c>
-      <c r="G58" t="s">
-        <v>351</v>
-      </c>
-      <c r="H58" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>353</v>
-      </c>
-      <c r="B59" t="s">
-        <v>354</v>
-      </c>
-      <c r="C59" t="s">
-        <v>355</v>
-      </c>
-      <c r="D59" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" t="s">
-        <v>218</v>
-      </c>
-      <c r="F59" t="s">
-        <v>356</v>
-      </c>
-      <c r="G59" t="s">
-        <v>357</v>
-      </c>
-      <c r="H59" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>359</v>
-      </c>
-      <c r="B60" t="s">
-        <v>336</v>
-      </c>
-      <c r="C60" t="s">
-        <v>360</v>
-      </c>
-      <c r="D60" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" t="s">
-        <v>218</v>
-      </c>
-      <c r="F60" t="s">
-        <v>361</v>
-      </c>
-      <c r="G60" t="s">
-        <v>362</v>
-      </c>
-      <c r="H60" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>364</v>
-      </c>
-      <c r="B61" t="s">
-        <v>42</v>
-      </c>
-      <c r="C61" t="s">
-        <v>365</v>
-      </c>
-      <c r="D61" t="s">
-        <v>11</v>
-      </c>
-      <c r="E61" t="s">
-        <v>218</v>
-      </c>
-      <c r="F61" t="s">
-        <v>366</v>
-      </c>
-      <c r="G61" t="s">
-        <v>367</v>
-      </c>
-      <c r="H61" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>369</v>
-      </c>
-      <c r="B62" t="s">
-        <v>342</v>
-      </c>
-      <c r="C62" t="s">
-        <v>370</v>
-      </c>
-      <c r="D62" t="s">
-        <v>11</v>
-      </c>
-      <c r="E62" t="s">
-        <v>218</v>
-      </c>
-      <c r="F62" t="s">
-        <v>371</v>
-      </c>
-      <c r="G62" t="s">
-        <v>372</v>
-      </c>
-      <c r="H62" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>374</v>
-      </c>
-      <c r="B63" t="s">
-        <v>375</v>
-      </c>
-      <c r="C63" t="s">
-        <v>376</v>
-      </c>
-      <c r="D63" t="s">
-        <v>11</v>
-      </c>
-      <c r="E63" t="s">
-        <v>344</v>
-      </c>
-      <c r="F63" t="s">
-        <v>377</v>
-      </c>
-      <c r="G63" t="s">
-        <v>378</v>
-      </c>
-      <c r="H63" t="s">
+      <c r="C94" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" t="s">
+        <v>550</v>
+      </c>
+      <c r="G94" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" t="s">
+        <v>323</v>
+      </c>
+      <c r="I94" t="s">
+        <v>551</v>
+      </c>
+      <c r="J94" t="s">
+        <v>552</v>
+      </c>
+      <c r="K94" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>554</v>
+      </c>
+      <c r="B95" t="s">
+        <v>555</v>
+      </c>
+      <c r="C95" t="s">
+        <v>13</v>
+      </c>
+      <c r="D95" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" t="s">
+        <v>556</v>
+      </c>
+      <c r="G95" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" t="s">
+        <v>323</v>
+      </c>
+      <c r="I95" t="s">
+        <v>557</v>
+      </c>
+      <c r="J95" t="s">
+        <v>558</v>
+      </c>
+      <c r="K95" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>560</v>
+      </c>
+      <c r="B96" t="s">
+        <v>537</v>
+      </c>
+      <c r="C96" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" t="s">
+        <v>561</v>
+      </c>
+      <c r="G96" t="s">
+        <v>15</v>
+      </c>
+      <c r="H96" t="s">
+        <v>323</v>
+      </c>
+      <c r="I96" t="s">
+        <v>562</v>
+      </c>
+      <c r="J96" t="s">
+        <v>563</v>
+      </c>
+      <c r="K96" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>565</v>
+      </c>
+      <c r="B97" t="s">
+        <v>104</v>
+      </c>
+      <c r="C97" t="s">
+        <v>13</v>
+      </c>
+      <c r="D97" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" t="s">
+        <v>566</v>
+      </c>
+      <c r="G97" t="s">
+        <v>15</v>
+      </c>
+      <c r="H97" t="s">
+        <v>323</v>
+      </c>
+      <c r="I97" t="s">
+        <v>567</v>
+      </c>
+      <c r="J97" t="s">
+        <v>568</v>
+      </c>
+      <c r="K97" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>570</v>
+      </c>
+      <c r="B98" t="s">
+        <v>543</v>
+      </c>
+      <c r="C98" t="s">
+        <v>13</v>
+      </c>
+      <c r="D98" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" t="s">
+        <v>13</v>
+      </c>
+      <c r="F98" t="s">
+        <v>571</v>
+      </c>
+      <c r="G98" t="s">
+        <v>15</v>
+      </c>
+      <c r="H98" t="s">
+        <v>323</v>
+      </c>
+      <c r="I98" t="s">
+        <v>572</v>
+      </c>
+      <c r="J98" t="s">
+        <v>573</v>
+      </c>
+      <c r="K98" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>575</v>
+      </c>
+      <c r="B99" t="s">
+        <v>576</v>
+      </c>
+      <c r="C99" t="s">
+        <v>13</v>
+      </c>
+      <c r="D99" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" t="s">
+        <v>577</v>
+      </c>
+      <c r="G99" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" t="s">
+        <v>545</v>
+      </c>
+      <c r="I99" t="s">
+        <v>578</v>
+      </c>
+      <c r="J99" t="s">
+        <v>579</v>
+      </c>
+      <c r="K99" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>581</v>
+      </c>
+      <c r="B100" t="s">
+        <v>543</v>
+      </c>
+      <c r="C100" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" t="s">
+        <v>582</v>
+      </c>
+      <c r="G100" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" t="s">
+        <v>323</v>
+      </c>
+      <c r="I100" t="s">
+        <v>583</v>
+      </c>
+      <c r="J100" t="s">
+        <v>584</v>
+      </c>
+      <c r="K100" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>586</v>
+      </c>
+      <c r="B101" t="s">
+        <v>537</v>
+      </c>
+      <c r="C101" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" t="s">
+        <v>587</v>
+      </c>
+      <c r="G101" t="s">
+        <v>15</v>
+      </c>
+      <c r="H101" t="s">
+        <v>323</v>
+      </c>
+      <c r="I101" t="s">
+        <v>588</v>
+      </c>
+      <c r="J101" t="s">
+        <v>589</v>
+      </c>
+      <c r="K101" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>591</v>
+      </c>
+      <c r="B102" t="s">
+        <v>592</v>
+      </c>
+      <c r="C102" t="s">
+        <v>13</v>
+      </c>
+      <c r="D102" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" t="s">
+        <v>593</v>
+      </c>
+      <c r="G102" t="s">
+        <v>15</v>
+      </c>
+      <c r="H102" t="s">
+        <v>323</v>
+      </c>
+      <c r="I102" t="s">
+        <v>594</v>
+      </c>
+      <c r="J102" t="s">
+        <v>595</v>
+      </c>
+      <c r="K102" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>597</v>
+      </c>
+      <c r="B103" t="s">
+        <v>543</v>
+      </c>
+      <c r="C103" t="s">
+        <v>13</v>
+      </c>
+      <c r="D103" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" t="s">
+        <v>598</v>
+      </c>
+      <c r="G103" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" t="s">
+        <v>323</v>
+      </c>
+      <c r="I103" t="s">
+        <v>599</v>
+      </c>
+      <c r="J103" t="s">
+        <v>600</v>
+      </c>
+      <c r="K103" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>602</v>
+      </c>
+      <c r="B104" t="s">
+        <v>537</v>
+      </c>
+      <c r="C104" t="s">
+        <v>13</v>
+      </c>
+      <c r="D104" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" t="s">
+        <v>603</v>
+      </c>
+      <c r="G104" t="s">
+        <v>15</v>
+      </c>
+      <c r="H104" t="s">
+        <v>604</v>
+      </c>
+      <c r="I104" t="s">
+        <v>605</v>
+      </c>
+      <c r="J104" t="s">
+        <v>606</v>
+      </c>
+      <c r="K104" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>608</v>
+      </c>
+      <c r="B105" t="s">
+        <v>543</v>
+      </c>
+      <c r="C105" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" t="s">
+        <v>13</v>
+      </c>
+      <c r="F105" t="s">
+        <v>609</v>
+      </c>
+      <c r="G105" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" t="s">
+        <v>545</v>
+      </c>
+      <c r="I105" t="s">
+        <v>610</v>
+      </c>
+      <c r="J105" t="s">
+        <v>611</v>
+      </c>
+      <c r="K105" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>613</v>
+      </c>
+      <c r="B106" t="s">
+        <v>543</v>
+      </c>
+      <c r="C106" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" t="s">
+        <v>13</v>
+      </c>
+      <c r="F106" t="s">
+        <v>614</v>
+      </c>
+      <c r="G106" t="s">
+        <v>15</v>
+      </c>
+      <c r="H106" t="s">
+        <v>323</v>
+      </c>
+      <c r="I106" t="s">
+        <v>615</v>
+      </c>
+      <c r="J106" t="s">
+        <v>616</v>
+      </c>
+      <c r="K106" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>618</v>
+      </c>
+      <c r="B107" t="s">
+        <v>537</v>
+      </c>
+      <c r="C107" t="s">
+        <v>13</v>
+      </c>
+      <c r="D107" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" t="s">
+        <v>13</v>
+      </c>
+      <c r="F107" t="s">
+        <v>619</v>
+      </c>
+      <c r="G107" t="s">
+        <v>15</v>
+      </c>
+      <c r="H107" t="s">
+        <v>604</v>
+      </c>
+      <c r="I107" t="s">
+        <v>620</v>
+      </c>
+      <c r="J107" t="s">
+        <v>621</v>
+      </c>
+      <c r="K107" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>623</v>
+      </c>
+      <c r="B108" t="s">
+        <v>104</v>
+      </c>
+      <c r="C108" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108" t="s">
+        <v>13</v>
+      </c>
+      <c r="E108" t="s">
+        <v>13</v>
+      </c>
+      <c r="F108" t="s">
+        <v>624</v>
+      </c>
+      <c r="G108" t="s">
+        <v>15</v>
+      </c>
+      <c r="H108" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>380</v>
-      </c>
-      <c r="B64" t="s">
-        <v>342</v>
-      </c>
-      <c r="C64" t="s">
-        <v>381</v>
-      </c>
-      <c r="D64" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" t="s">
-        <v>218</v>
-      </c>
-      <c r="F64" t="s">
-        <v>382</v>
-      </c>
-      <c r="G64" t="s">
-        <v>383</v>
-      </c>
-      <c r="H64" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>385</v>
-      </c>
-      <c r="B65" t="s">
-        <v>336</v>
-      </c>
-      <c r="C65" t="s">
-        <v>386</v>
-      </c>
-      <c r="D65" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" t="s">
-        <v>218</v>
-      </c>
-      <c r="F65" t="s">
-        <v>387</v>
-      </c>
-      <c r="G65" t="s">
-        <v>388</v>
-      </c>
-      <c r="H65" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>390</v>
-      </c>
-      <c r="B66" t="s">
-        <v>391</v>
-      </c>
-      <c r="C66" t="s">
-        <v>392</v>
-      </c>
-      <c r="D66" t="s">
-        <v>11</v>
-      </c>
-      <c r="E66" t="s">
-        <v>218</v>
-      </c>
-      <c r="F66" t="s">
-        <v>393</v>
-      </c>
-      <c r="G66" t="s">
-        <v>394</v>
-      </c>
-      <c r="H66" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>396</v>
-      </c>
-      <c r="B67" t="s">
-        <v>342</v>
-      </c>
-      <c r="C67" t="s">
-        <v>397</v>
-      </c>
-      <c r="D67" t="s">
-        <v>11</v>
-      </c>
-      <c r="E67" t="s">
-        <v>218</v>
-      </c>
-      <c r="F67" t="s">
-        <v>398</v>
-      </c>
-      <c r="G67" t="s">
-        <v>399</v>
-      </c>
-      <c r="H67" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>401</v>
-      </c>
-      <c r="B68" t="s">
-        <v>336</v>
-      </c>
-      <c r="C68" t="s">
-        <v>402</v>
-      </c>
-      <c r="D68" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" t="s">
-        <v>403</v>
-      </c>
-      <c r="F68" t="s">
-        <v>404</v>
-      </c>
-      <c r="G68" t="s">
-        <v>405</v>
-      </c>
-      <c r="H68" t="s">
+      <c r="I108" t="s">
+        <v>625</v>
+      </c>
+      <c r="J108" t="s">
+        <v>626</v>
+      </c>
+      <c r="K108" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>628</v>
+      </c>
+      <c r="B109" t="s">
+        <v>104</v>
+      </c>
+      <c r="C109" t="s">
+        <v>13</v>
+      </c>
+      <c r="D109" t="s">
+        <v>13</v>
+      </c>
+      <c r="E109" t="s">
+        <v>13</v>
+      </c>
+      <c r="F109" t="s">
+        <v>629</v>
+      </c>
+      <c r="G109" t="s">
+        <v>15</v>
+      </c>
+      <c r="H109" t="s">
+        <v>379</v>
+      </c>
+      <c r="I109" t="s">
+        <v>630</v>
+      </c>
+      <c r="J109" t="s">
+        <v>631</v>
+      </c>
+      <c r="K109" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>633</v>
+      </c>
+      <c r="B110" t="s">
+        <v>104</v>
+      </c>
+      <c r="C110" t="s">
+        <v>13</v>
+      </c>
+      <c r="D110" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" t="s">
+        <v>13</v>
+      </c>
+      <c r="F110" t="s">
+        <v>634</v>
+      </c>
+      <c r="G110" t="s">
+        <v>15</v>
+      </c>
+      <c r="H110" t="s">
+        <v>379</v>
+      </c>
+      <c r="I110" t="s">
+        <v>635</v>
+      </c>
+      <c r="J110" t="s">
+        <v>636</v>
+      </c>
+      <c r="K110" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>638</v>
+      </c>
+      <c r="B111" t="s">
+        <v>104</v>
+      </c>
+      <c r="C111" t="s">
+        <v>13</v>
+      </c>
+      <c r="D111" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" t="s">
+        <v>13</v>
+      </c>
+      <c r="F111" t="s">
+        <v>639</v>
+      </c>
+      <c r="G111" t="s">
+        <v>15</v>
+      </c>
+      <c r="H111" t="s">
+        <v>379</v>
+      </c>
+      <c r="I111" t="s">
+        <v>640</v>
+      </c>
+      <c r="J111" t="s">
+        <v>641</v>
+      </c>
+      <c r="K111" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>643</v>
+      </c>
+      <c r="B112" t="s">
+        <v>104</v>
+      </c>
+      <c r="C112" t="s">
+        <v>13</v>
+      </c>
+      <c r="D112" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" t="s">
+        <v>13</v>
+      </c>
+      <c r="F112" t="s">
+        <v>644</v>
+      </c>
+      <c r="G112" t="s">
+        <v>15</v>
+      </c>
+      <c r="H112" t="s">
+        <v>532</v>
+      </c>
+      <c r="I112" t="s">
+        <v>645</v>
+      </c>
+      <c r="J112" t="s">
+        <v>646</v>
+      </c>
+      <c r="K112" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>648</v>
+      </c>
+      <c r="B113" t="s">
+        <v>104</v>
+      </c>
+      <c r="C113" t="s">
+        <v>13</v>
+      </c>
+      <c r="D113" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" t="s">
+        <v>649</v>
+      </c>
+      <c r="G113" t="s">
+        <v>15</v>
+      </c>
+      <c r="H113" t="s">
+        <v>379</v>
+      </c>
+      <c r="I113" t="s">
+        <v>650</v>
+      </c>
+      <c r="J113" t="s">
+        <v>651</v>
+      </c>
+      <c r="K113" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>653</v>
+      </c>
+      <c r="B114" t="s">
+        <v>654</v>
+      </c>
+      <c r="C114" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>407</v>
-      </c>
-      <c r="B69" t="s">
-        <v>342</v>
-      </c>
-      <c r="C69" t="s">
-        <v>408</v>
-      </c>
-      <c r="D69" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" t="s">
-        <v>344</v>
-      </c>
-      <c r="F69" t="s">
-        <v>409</v>
-      </c>
-      <c r="G69" t="s">
-        <v>410</v>
-      </c>
-      <c r="H69" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>412</v>
-      </c>
-      <c r="B70" t="s">
-        <v>342</v>
-      </c>
-      <c r="C70" t="s">
+      <c r="D114" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" t="s">
+        <v>655</v>
+      </c>
+      <c r="F114" t="s">
+        <v>656</v>
+      </c>
+      <c r="G114" t="s">
+        <v>15</v>
+      </c>
+      <c r="H114" t="s">
+        <v>422</v>
+      </c>
+      <c r="I114" t="s">
+        <v>657</v>
+      </c>
+      <c r="J114" t="s">
+        <v>658</v>
+      </c>
+      <c r="K114" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>660</v>
+      </c>
+      <c r="B115" t="s">
+        <v>654</v>
+      </c>
+      <c r="C115" t="s">
         <v>413</v>
       </c>
-      <c r="D70" t="s">
-        <v>11</v>
-      </c>
-      <c r="E70" t="s">
-        <v>218</v>
-      </c>
-      <c r="F70" t="s">
-        <v>414</v>
-      </c>
-      <c r="G70" t="s">
-        <v>415</v>
-      </c>
-      <c r="H70" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>417</v>
-      </c>
-      <c r="B71" t="s">
-        <v>336</v>
-      </c>
-      <c r="C71" t="s">
-        <v>418</v>
-      </c>
-      <c r="D71" t="s">
-        <v>11</v>
-      </c>
-      <c r="E71" t="s">
-        <v>403</v>
-      </c>
-      <c r="F71" t="s">
-        <v>419</v>
-      </c>
-      <c r="G71" t="s">
-        <v>420</v>
-      </c>
-      <c r="H71" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="D115" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" t="s">
+        <v>655</v>
+      </c>
+      <c r="F115" t="s">
+        <v>661</v>
+      </c>
+      <c r="G115" t="s">
+        <v>15</v>
+      </c>
+      <c r="H115" t="s">
         <v>422</v>
       </c>
-      <c r="B72" t="s">
-        <v>42</v>
-      </c>
-      <c r="C72" t="s">
-        <v>423</v>
-      </c>
-      <c r="D72" t="s">
-        <v>11</v>
-      </c>
-      <c r="E72" t="s">
-        <v>274</v>
-      </c>
-      <c r="F72" t="s">
-        <v>424</v>
-      </c>
-      <c r="G72" t="s">
-        <v>425</v>
-      </c>
-      <c r="H72" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>427</v>
-      </c>
-      <c r="B73" t="s">
-        <v>42</v>
-      </c>
-      <c r="C73" t="s">
-        <v>428</v>
-      </c>
-      <c r="D73" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" t="s">
-        <v>274</v>
-      </c>
-      <c r="F73" t="s">
-        <v>429</v>
-      </c>
-      <c r="G73" t="s">
-        <v>430</v>
-      </c>
-      <c r="H73" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>432</v>
-      </c>
-      <c r="B74" t="s">
-        <v>42</v>
-      </c>
-      <c r="C74" t="s">
-        <v>433</v>
-      </c>
-      <c r="D74" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" t="s">
-        <v>274</v>
-      </c>
-      <c r="F74" t="s">
-        <v>434</v>
-      </c>
-      <c r="G74" t="s">
-        <v>435</v>
-      </c>
-      <c r="H74" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>437</v>
-      </c>
-      <c r="B75" t="s">
-        <v>42</v>
-      </c>
-      <c r="C75" t="s">
-        <v>438</v>
-      </c>
-      <c r="D75" t="s">
-        <v>11</v>
-      </c>
-      <c r="E75" t="s">
-        <v>274</v>
-      </c>
-      <c r="F75" t="s">
-        <v>439</v>
-      </c>
-      <c r="G75" t="s">
-        <v>440</v>
-      </c>
-      <c r="H75" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>442</v>
-      </c>
-      <c r="B76" t="s">
-        <v>42</v>
-      </c>
-      <c r="C76" t="s">
-        <v>443</v>
-      </c>
-      <c r="D76" t="s">
-        <v>11</v>
-      </c>
-      <c r="E76" t="s">
-        <v>331</v>
-      </c>
-      <c r="F76" t="s">
-        <v>444</v>
-      </c>
-      <c r="G76" t="s">
-        <v>445</v>
-      </c>
-      <c r="H76" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>447</v>
-      </c>
-      <c r="B77" t="s">
-        <v>42</v>
-      </c>
-      <c r="C77" t="s">
-        <v>448</v>
-      </c>
-      <c r="D77" t="s">
-        <v>11</v>
-      </c>
-      <c r="E77" t="s">
-        <v>274</v>
-      </c>
-      <c r="F77" t="s">
-        <v>449</v>
-      </c>
-      <c r="G77" t="s">
-        <v>450</v>
-      </c>
-      <c r="H77" t="s">
-        <v>451</v>
+      <c r="I115" t="s">
+        <v>662</v>
+      </c>
+      <c r="J115" t="s">
+        <v>663</v>
+      </c>
+      <c r="K115" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>665</v>
+      </c>
+      <c r="B116" t="s">
+        <v>666</v>
+      </c>
+      <c r="C116" t="s">
+        <v>667</v>
+      </c>
+      <c r="D116" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" t="s">
+        <v>668</v>
+      </c>
+      <c r="F116" t="s">
+        <v>669</v>
+      </c>
+      <c r="G116" t="s">
+        <v>15</v>
+      </c>
+      <c r="H116" t="s">
+        <v>422</v>
+      </c>
+      <c r="I116" t="s">
+        <v>670</v>
+      </c>
+      <c r="J116" t="s">
+        <v>671</v>
+      </c>
+      <c r="K116" t="s">
+        <v>672</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-contact.report.xlsx
+++ b/tools/importer/reports/import-contact.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="678">
   <si>
     <t>_reportFile</t>
   </si>
@@ -73,6 +73,27 @@
     <t>https://www.highmark.com/because-life</t>
   </si>
   <si>
+    <t>contact-thank-you.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>contact-thank-you</t>
+  </si>
+  <si>
+    <t>fraud-thank-you</t>
+  </si>
+  <si>
+    <t>2026-10-14T08:30:39.378Z</t>
+  </si>
+  <si>
+    <t>Thank You</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/contact-thank-you</t>
+  </si>
+  <si>
     <t>contact.report.json</t>
   </si>
   <si>
@@ -82,7 +103,7 @@
     <t>contact</t>
   </si>
   <si>
-    <t>2026-10-14T08:30:32.469Z</t>
+    <t>2026-10-14T09:06:59.963Z</t>
   </si>
   <si>
     <t>Contact Highmark</t>
@@ -113,12 +134,6 @@
   </si>
   <si>
     <t>fraud-thank-you.report.json</t>
-  </si>
-  <si>
-    <t>[]</t>
-  </si>
-  <si>
-    <t>fraud-thank-you</t>
   </si>
   <si>
     <t>2026-10-14T07:13:24.168Z</t>
@@ -2418,7 +2433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K116"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -2523,24 +2538,24 @@
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -2552,7 +2567,7 @@
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -2593,24 +2608,24 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -2622,112 +2637,112 @@
         <v>13</v>
       </c>
       <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" t="s">
         <v>41</v>
       </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
         <v>42</v>
       </c>
-      <c r="I6" t="s">
+      <c r="K6" t="s">
         <v>43</v>
-      </c>
-      <c r="J6" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
         <v>46</v>
       </c>
-      <c r="B7" t="s">
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
         <v>47</v>
       </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="I7" t="s">
         <v>48</v>
       </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>49</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>50</v>
-      </c>
-      <c r="K7" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" t="s">
         <v>52</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
         <v>53</v>
       </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
         <v>54</v>
       </c>
-      <c r="G8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
         <v>55</v>
       </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
         <v>56</v>
-      </c>
-      <c r="J8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
         <v>59</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
@@ -2750,7 +2765,7 @@
         <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
@@ -2774,18 +2789,18 @@
         <v>66</v>
       </c>
       <c r="J10" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="K10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
@@ -2803,42 +2818,42 @@
         <v>15</v>
       </c>
       <c r="H11" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" t="s">
         <v>71</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" t="s">
         <v>72</v>
-      </c>
-      <c r="J11" t="s">
-        <v>73</v>
-      </c>
-      <c r="K11" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
         <v>75</v>
       </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
         <v>76</v>
-      </c>
-      <c r="G12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" t="s">
-        <v>71</v>
       </c>
       <c r="I12" t="s">
         <v>77</v>
@@ -2855,7 +2870,7 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
@@ -2873,118 +2888,118 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" t="s">
         <v>82</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>83</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>84</v>
-      </c>
-      <c r="K13" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
         <v>86</v>
       </c>
-      <c r="B14" t="s">
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s">
         <v>87</v>
       </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="I14" t="s">
         <v>88</v>
       </c>
-      <c r="G14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>89</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>90</v>
-      </c>
-      <c r="K14" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" t="s">
         <v>92</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
         <v>93</v>
       </c>
-      <c r="C15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" t="s">
         <v>94</v>
       </c>
-      <c r="G15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>95</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>96</v>
-      </c>
-      <c r="K15" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" t="s">
         <v>98</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
         <v>99</v>
       </c>
-      <c r="C16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>47</v>
+      </c>
+      <c r="I16" t="s">
         <v>100</v>
       </c>
-      <c r="G16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" t="s">
-        <v>100</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>101</v>
-      </c>
-      <c r="J16" t="s">
-        <v>13</v>
       </c>
       <c r="K16" t="s">
         <v>102</v>
@@ -3013,77 +3028,77 @@
         <v>15</v>
       </c>
       <c r="H17" t="s">
+        <v>105</v>
+      </c>
+      <c r="I17" t="s">
         <v>106</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" t="s">
         <v>107</v>
-      </c>
-      <c r="J17" t="s">
-        <v>108</v>
-      </c>
-      <c r="K17" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
         <v>110</v>
       </c>
-      <c r="B18" t="s">
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
         <v>111</v>
       </c>
-      <c r="C18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="I18" t="s">
         <v>112</v>
       </c>
-      <c r="G18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" t="s">
+      <c r="J18" t="s">
         <v>113</v>
       </c>
-      <c r="I18" t="s">
+      <c r="K18" t="s">
         <v>114</v>
-      </c>
-      <c r="J18" t="s">
-        <v>115</v>
-      </c>
-      <c r="K18" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
         <v>117</v>
       </c>
-      <c r="B19" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" t="s">
         <v>118</v>
-      </c>
-      <c r="G19" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" t="s">
-        <v>106</v>
       </c>
       <c r="I19" t="s">
         <v>119</v>
@@ -3100,270 +3115,270 @@
         <v>122</v>
       </c>
       <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
         <v>123</v>
       </c>
-      <c r="C20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" t="s">
+        <v>111</v>
+      </c>
+      <c r="I20" t="s">
         <v>124</v>
       </c>
-      <c r="G20" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>125</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>126</v>
-      </c>
-      <c r="K20" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" t="s">
         <v>128</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
         <v>129</v>
       </c>
-      <c r="C21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s">
         <v>130</v>
       </c>
-      <c r="G21" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="J21" t="s">
         <v>131</v>
       </c>
-      <c r="I21" t="s">
+      <c r="K21" t="s">
         <v>132</v>
-      </c>
-      <c r="J21" t="s">
-        <v>133</v>
-      </c>
-      <c r="K21" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s">
         <v>135</v>
       </c>
-      <c r="B22" t="s">
+      <c r="G22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" t="s">
         <v>136</v>
       </c>
-      <c r="C22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="I22" t="s">
         <v>137</v>
       </c>
-      <c r="G22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" t="s">
-        <v>131</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>138</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>139</v>
-      </c>
-      <c r="K22" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" t="s">
         <v>141</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" t="s">
         <v>142</v>
       </c>
-      <c r="C23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" t="s">
+        <v>136</v>
+      </c>
+      <c r="I23" t="s">
         <v>143</v>
       </c>
-      <c r="G23" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" t="s">
-        <v>131</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>144</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>145</v>
-      </c>
-      <c r="K23" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" t="s">
         <v>147</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" t="s">
         <v>148</v>
       </c>
-      <c r="C24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" t="s">
+        <v>136</v>
+      </c>
+      <c r="I24" t="s">
         <v>149</v>
       </c>
-      <c r="G24" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" t="s">
-        <v>131</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>150</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>151</v>
-      </c>
-      <c r="K24" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>152</v>
+      </c>
+      <c r="B25" t="s">
         <v>153</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" t="s">
         <v>154</v>
       </c>
-      <c r="C25" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" t="s">
+        <v>136</v>
+      </c>
+      <c r="I25" t="s">
         <v>155</v>
       </c>
-      <c r="G25" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" t="s">
-        <v>131</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>156</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>157</v>
-      </c>
-      <c r="K25" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" t="s">
         <v>159</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
         <v>160</v>
       </c>
-      <c r="C26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" t="s">
+        <v>136</v>
+      </c>
+      <c r="I26" t="s">
         <v>161</v>
       </c>
-      <c r="G26" t="s">
-        <v>15</v>
-      </c>
-      <c r="H26" t="s">
+      <c r="J26" t="s">
         <v>162</v>
       </c>
-      <c r="I26" t="s">
+      <c r="K26" t="s">
         <v>163</v>
-      </c>
-      <c r="J26" t="s">
-        <v>164</v>
-      </c>
-      <c r="K26" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
         <v>166</v>
       </c>
-      <c r="B27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27">
-        <v>2</v>
-      </c>
-      <c r="E27" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" t="s">
         <v>167</v>
-      </c>
-      <c r="G27" t="s">
-        <v>15</v>
-      </c>
-      <c r="H27" t="s">
-        <v>13</v>
       </c>
       <c r="I27" t="s">
         <v>168</v>
@@ -3380,101 +3395,101 @@
         <v>171</v>
       </c>
       <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s">
         <v>172</v>
       </c>
-      <c r="C28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" t="s">
         <v>173</v>
       </c>
-      <c r="G28" t="s">
-        <v>15</v>
-      </c>
-      <c r="H28" t="s">
+      <c r="J28" t="s">
         <v>174</v>
       </c>
-      <c r="I28" t="s">
+      <c r="K28" t="s">
         <v>175</v>
-      </c>
-      <c r="J28" t="s">
-        <v>176</v>
-      </c>
-      <c r="K28" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>176</v>
+      </c>
+      <c r="B29" t="s">
+        <v>177</v>
+      </c>
+      <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" t="s">
         <v>178</v>
       </c>
-      <c r="B29" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" t="s">
         <v>179</v>
       </c>
-      <c r="G29" t="s">
-        <v>15</v>
-      </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>180</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>181</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>182</v>
-      </c>
-      <c r="K29" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>183</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" t="s">
         <v>184</v>
       </c>
-      <c r="B30" t="s">
-        <v>111</v>
-      </c>
-      <c r="C30" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" t="s">
         <v>185</v>
       </c>
-      <c r="G30" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>186</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>187</v>
-      </c>
-      <c r="J30" t="s">
-        <v>13</v>
       </c>
       <c r="K30" t="s">
         <v>188</v>
@@ -3485,7 +3500,7 @@
         <v>189</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
         <v>13</v>
@@ -3509,106 +3524,106 @@
         <v>192</v>
       </c>
       <c r="J31" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" t="s">
         <v>193</v>
-      </c>
-      <c r="K31" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>194</v>
+      </c>
+      <c r="B32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" t="s">
         <v>195</v>
       </c>
-      <c r="B32" t="s">
+      <c r="G32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" t="s">
         <v>196</v>
       </c>
-      <c r="C32" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="I32" t="s">
         <v>197</v>
       </c>
-      <c r="G32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H32" t="s">
+      <c r="J32" t="s">
         <v>198</v>
       </c>
-      <c r="I32" t="s">
+      <c r="K32" t="s">
         <v>199</v>
-      </c>
-      <c r="J32" t="s">
-        <v>200</v>
-      </c>
-      <c r="K32" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>200</v>
+      </c>
+      <c r="B33" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" t="s">
         <v>202</v>
       </c>
-      <c r="B33" t="s">
+      <c r="G33" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" t="s">
         <v>203</v>
       </c>
-      <c r="C33" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="I33" t="s">
         <v>204</v>
       </c>
-      <c r="G33" t="s">
-        <v>15</v>
-      </c>
-      <c r="H33" t="s">
+      <c r="J33" t="s">
         <v>205</v>
       </c>
-      <c r="I33" t="s">
+      <c r="K33" t="s">
         <v>206</v>
-      </c>
-      <c r="J33" t="s">
-        <v>207</v>
-      </c>
-      <c r="K33" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>207</v>
+      </c>
+      <c r="B34" t="s">
+        <v>208</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" t="s">
         <v>209</v>
       </c>
-      <c r="B34" t="s">
-        <v>196</v>
-      </c>
-      <c r="C34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" t="s">
         <v>210</v>
-      </c>
-      <c r="G34" t="s">
-        <v>15</v>
-      </c>
-      <c r="H34" t="s">
-        <v>198</v>
       </c>
       <c r="I34" t="s">
         <v>211</v>
@@ -3625,235 +3640,235 @@
         <v>214</v>
       </c>
       <c r="B35" t="s">
+        <v>201</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" t="s">
         <v>215</v>
       </c>
-      <c r="C35" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" t="s">
+        <v>203</v>
+      </c>
+      <c r="I35" t="s">
         <v>216</v>
       </c>
-      <c r="G35" t="s">
-        <v>15</v>
-      </c>
-      <c r="H35" t="s">
+      <c r="J35" t="s">
         <v>217</v>
       </c>
-      <c r="I35" t="s">
+      <c r="K35" t="s">
         <v>218</v>
-      </c>
-      <c r="J35" t="s">
-        <v>219</v>
-      </c>
-      <c r="K35" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>219</v>
+      </c>
+      <c r="B36" t="s">
+        <v>220</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" t="s">
         <v>221</v>
       </c>
-      <c r="B36" t="s">
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
         <v>222</v>
       </c>
-      <c r="C36" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="I36" t="s">
         <v>223</v>
       </c>
-      <c r="G36" t="s">
-        <v>15</v>
-      </c>
-      <c r="H36" t="s">
-        <v>82</v>
-      </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
         <v>224</v>
       </c>
-      <c r="J36" t="s">
+      <c r="K36" t="s">
         <v>225</v>
-      </c>
-      <c r="K36" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>226</v>
+      </c>
+      <c r="B37" t="s">
         <v>227</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" t="s">
         <v>228</v>
       </c>
-      <c r="C37" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" t="s">
+        <v>87</v>
+      </c>
+      <c r="I37" t="s">
         <v>229</v>
       </c>
-      <c r="G37" t="s">
-        <v>15</v>
-      </c>
-      <c r="H37" t="s">
+      <c r="J37" t="s">
         <v>230</v>
       </c>
-      <c r="I37" t="s">
+      <c r="K37" t="s">
         <v>231</v>
-      </c>
-      <c r="J37" t="s">
-        <v>232</v>
-      </c>
-      <c r="K37" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>232</v>
+      </c>
+      <c r="B38" t="s">
+        <v>233</v>
+      </c>
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" t="s">
         <v>234</v>
       </c>
-      <c r="B38" t="s">
+      <c r="G38" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" t="s">
         <v>235</v>
       </c>
-      <c r="C38" t="s">
+      <c r="I38" t="s">
         <v>236</v>
       </c>
-      <c r="D38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="J38" t="s">
         <v>237</v>
       </c>
-      <c r="G38" t="s">
-        <v>15</v>
-      </c>
-      <c r="H38" t="s">
+      <c r="K38" t="s">
         <v>238</v>
-      </c>
-      <c r="I38" t="s">
-        <v>239</v>
-      </c>
-      <c r="J38" t="s">
-        <v>240</v>
-      </c>
-      <c r="K38" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>239</v>
+      </c>
+      <c r="B39" t="s">
+        <v>240</v>
+      </c>
+      <c r="C39" t="s">
+        <v>241</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" t="s">
         <v>242</v>
       </c>
-      <c r="B39" t="s">
+      <c r="G39" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" t="s">
         <v>243</v>
       </c>
-      <c r="C39" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="I39" t="s">
         <v>244</v>
       </c>
-      <c r="G39" t="s">
-        <v>15</v>
-      </c>
-      <c r="H39" t="s">
+      <c r="J39" t="s">
         <v>245</v>
       </c>
-      <c r="I39" t="s">
+      <c r="K39" t="s">
         <v>246</v>
-      </c>
-      <c r="J39" t="s">
-        <v>247</v>
-      </c>
-      <c r="K39" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>247</v>
+      </c>
+      <c r="B40" t="s">
+        <v>248</v>
+      </c>
+      <c r="C40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" t="s">
         <v>249</v>
       </c>
-      <c r="B40" t="s">
+      <c r="G40" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" t="s">
         <v>250</v>
       </c>
-      <c r="C40" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="I40" t="s">
         <v>251</v>
       </c>
-      <c r="G40" t="s">
-        <v>15</v>
-      </c>
-      <c r="H40" t="s">
+      <c r="J40" t="s">
         <v>252</v>
       </c>
-      <c r="I40" t="s">
+      <c r="K40" t="s">
         <v>253</v>
-      </c>
-      <c r="J40" t="s">
-        <v>254</v>
-      </c>
-      <c r="K40" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>254</v>
+      </c>
+      <c r="B41" t="s">
+        <v>255</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" t="s">
         <v>256</v>
       </c>
-      <c r="B41" t="s">
-        <v>104</v>
-      </c>
-      <c r="C41" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" t="s">
         <v>257</v>
-      </c>
-      <c r="G41" t="s">
-        <v>15</v>
-      </c>
-      <c r="H41" t="s">
-        <v>106</v>
       </c>
       <c r="I41" t="s">
         <v>258</v>
@@ -3870,7 +3885,7 @@
         <v>261</v>
       </c>
       <c r="B42" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C42" t="s">
         <v>13</v>
@@ -3888,7 +3903,7 @@
         <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I42" t="s">
         <v>263</v>
@@ -3905,7 +3920,7 @@
         <v>266</v>
       </c>
       <c r="B43" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
@@ -3923,7 +3938,7 @@
         <v>15</v>
       </c>
       <c r="H43" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I43" t="s">
         <v>268</v>
@@ -3940,42 +3955,42 @@
         <v>271</v>
       </c>
       <c r="B44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" t="s">
         <v>272</v>
       </c>
-      <c r="C44" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" t="s">
+        <v>111</v>
+      </c>
+      <c r="I44" t="s">
         <v>273</v>
       </c>
-      <c r="G44" t="s">
-        <v>15</v>
-      </c>
-      <c r="H44" t="s">
+      <c r="J44" t="s">
         <v>274</v>
       </c>
-      <c r="I44" t="s">
+      <c r="K44" t="s">
         <v>275</v>
-      </c>
-      <c r="J44" t="s">
-        <v>13</v>
-      </c>
-      <c r="K44" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>276</v>
+      </c>
+      <c r="B45" t="s">
         <v>277</v>
-      </c>
-      <c r="B45" t="s">
-        <v>104</v>
       </c>
       <c r="C45" t="s">
         <v>13</v>
@@ -3993,13 +4008,13 @@
         <v>15</v>
       </c>
       <c r="H45" t="s">
-        <v>106</v>
+        <v>279</v>
       </c>
       <c r="I45" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J45" t="s">
-        <v>280</v>
+        <v>13</v>
       </c>
       <c r="K45" t="s">
         <v>281</v>
@@ -4010,7 +4025,7 @@
         <v>282</v>
       </c>
       <c r="B46" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C46" t="s">
         <v>13</v>
@@ -4028,7 +4043,7 @@
         <v>15</v>
       </c>
       <c r="H46" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I46" t="s">
         <v>284</v>
@@ -4045,235 +4060,235 @@
         <v>287</v>
       </c>
       <c r="B47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" t="s">
         <v>288</v>
       </c>
-      <c r="C47" t="s">
-        <v>13</v>
-      </c>
-      <c r="D47" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" t="s">
-        <v>13</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" t="s">
+        <v>111</v>
+      </c>
+      <c r="I47" t="s">
         <v>289</v>
       </c>
-      <c r="G47" t="s">
-        <v>15</v>
-      </c>
-      <c r="H47" t="s">
+      <c r="J47" t="s">
         <v>290</v>
       </c>
-      <c r="I47" t="s">
+      <c r="K47" t="s">
         <v>291</v>
-      </c>
-      <c r="J47" t="s">
-        <v>292</v>
-      </c>
-      <c r="K47" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>292</v>
+      </c>
+      <c r="B48" t="s">
+        <v>293</v>
+      </c>
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" t="s">
         <v>294</v>
       </c>
-      <c r="B48" t="s">
+      <c r="G48" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" t="s">
         <v>295</v>
       </c>
-      <c r="C48" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="I48" t="s">
         <v>296</v>
       </c>
-      <c r="G48" t="s">
-        <v>15</v>
-      </c>
-      <c r="H48" t="s">
+      <c r="J48" t="s">
         <v>297</v>
       </c>
-      <c r="I48" t="s">
+      <c r="K48" t="s">
         <v>298</v>
-      </c>
-      <c r="J48" t="s">
-        <v>299</v>
-      </c>
-      <c r="K48" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>299</v>
+      </c>
+      <c r="B49" t="s">
+        <v>300</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" t="s">
         <v>301</v>
       </c>
-      <c r="B49" t="s">
+      <c r="G49" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" t="s">
         <v>302</v>
       </c>
-      <c r="C49" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="I49" t="s">
         <v>303</v>
       </c>
-      <c r="G49" t="s">
-        <v>15</v>
-      </c>
-      <c r="H49" t="s">
+      <c r="J49" t="s">
         <v>304</v>
       </c>
-      <c r="I49" t="s">
+      <c r="K49" t="s">
         <v>305</v>
-      </c>
-      <c r="J49" t="s">
-        <v>306</v>
-      </c>
-      <c r="K49" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>306</v>
+      </c>
+      <c r="B50" t="s">
+        <v>307</v>
+      </c>
+      <c r="C50" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" t="s">
         <v>308</v>
       </c>
-      <c r="B50" t="s">
+      <c r="G50" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" t="s">
         <v>309</v>
       </c>
-      <c r="C50" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="I50" t="s">
         <v>310</v>
       </c>
-      <c r="G50" t="s">
-        <v>15</v>
-      </c>
-      <c r="H50" t="s">
-        <v>297</v>
-      </c>
-      <c r="I50" t="s">
+      <c r="J50" t="s">
         <v>311</v>
       </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
         <v>312</v>
-      </c>
-      <c r="K50" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>313</v>
+      </c>
+      <c r="B51" t="s">
         <v>314</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" t="s">
         <v>315</v>
       </c>
-      <c r="C51" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" t="s">
-        <v>13</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" t="s">
+        <v>302</v>
+      </c>
+      <c r="I51" t="s">
         <v>316</v>
       </c>
-      <c r="G51" t="s">
-        <v>15</v>
-      </c>
-      <c r="H51" t="s">
+      <c r="J51" t="s">
         <v>317</v>
       </c>
-      <c r="I51" t="s">
+      <c r="K51" t="s">
         <v>318</v>
-      </c>
-      <c r="J51" t="s">
-        <v>319</v>
-      </c>
-      <c r="K51" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>319</v>
+      </c>
+      <c r="B52" t="s">
+        <v>320</v>
+      </c>
+      <c r="C52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" t="s">
         <v>321</v>
       </c>
-      <c r="B52" t="s">
-        <v>104</v>
-      </c>
-      <c r="C52" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" t="s">
         <v>322</v>
       </c>
-      <c r="G52" t="s">
-        <v>15</v>
-      </c>
-      <c r="H52" t="s">
+      <c r="I52" t="s">
         <v>323</v>
       </c>
-      <c r="I52" t="s">
+      <c r="J52" t="s">
         <v>324</v>
       </c>
-      <c r="J52" t="s">
+      <c r="K52" t="s">
         <v>325</v>
-      </c>
-      <c r="K52" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>326</v>
+      </c>
+      <c r="B53" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" t="s">
         <v>327</v>
       </c>
-      <c r="B53" t="s">
-        <v>104</v>
-      </c>
-      <c r="C53" t="s">
-        <v>13</v>
-      </c>
-      <c r="D53" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" t="s">
         <v>328</v>
-      </c>
-      <c r="G53" t="s">
-        <v>15</v>
-      </c>
-      <c r="H53" t="s">
-        <v>323</v>
       </c>
       <c r="I53" t="s">
         <v>329</v>
@@ -4290,112 +4305,112 @@
         <v>332</v>
       </c>
       <c r="B54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" t="s">
         <v>333</v>
       </c>
-      <c r="C54" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" t="s">
+        <v>328</v>
+      </c>
+      <c r="I54" t="s">
         <v>334</v>
       </c>
-      <c r="G54" t="s">
-        <v>15</v>
-      </c>
-      <c r="H54" t="s">
-        <v>323</v>
-      </c>
-      <c r="I54" t="s">
+      <c r="J54" t="s">
         <v>335</v>
       </c>
-      <c r="J54" t="s">
+      <c r="K54" t="s">
         <v>336</v>
-      </c>
-      <c r="K54" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>337</v>
+      </c>
+      <c r="B55" t="s">
         <v>338</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" t="s">
         <v>339</v>
       </c>
-      <c r="C55" t="s">
-        <v>13</v>
-      </c>
-      <c r="D55" t="s">
-        <v>13</v>
-      </c>
-      <c r="E55" t="s">
-        <v>13</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" t="s">
+        <v>328</v>
+      </c>
+      <c r="I55" t="s">
         <v>340</v>
       </c>
-      <c r="G55" t="s">
-        <v>15</v>
-      </c>
-      <c r="H55" t="s">
-        <v>217</v>
-      </c>
-      <c r="I55" t="s">
+      <c r="J55" t="s">
         <v>341</v>
       </c>
-      <c r="J55" t="s">
+      <c r="K55" t="s">
         <v>342</v>
-      </c>
-      <c r="K55" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>343</v>
+      </c>
+      <c r="B56" t="s">
         <v>344</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" t="s">
         <v>345</v>
       </c>
-      <c r="C56" t="s">
-        <v>13</v>
-      </c>
-      <c r="D56" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" t="s">
+        <v>222</v>
+      </c>
+      <c r="I56" t="s">
         <v>346</v>
       </c>
-      <c r="G56" t="s">
-        <v>15</v>
-      </c>
-      <c r="H56" t="s">
-        <v>230</v>
-      </c>
-      <c r="I56" t="s">
+      <c r="J56" t="s">
         <v>347</v>
       </c>
-      <c r="J56" t="s">
+      <c r="K56" t="s">
         <v>348</v>
-      </c>
-      <c r="K56" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>349</v>
+      </c>
+      <c r="B57" t="s">
         <v>350</v>
-      </c>
-      <c r="B57" t="s">
-        <v>345</v>
       </c>
       <c r="C57" t="s">
         <v>13</v>
@@ -4413,7 +4428,7 @@
         <v>15</v>
       </c>
       <c r="H57" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I57" t="s">
         <v>352</v>
@@ -4430,7 +4445,7 @@
         <v>355</v>
       </c>
       <c r="B58" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C58" t="s">
         <v>13</v>
@@ -4448,7 +4463,7 @@
         <v>15</v>
       </c>
       <c r="H58" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I58" t="s">
         <v>357</v>
@@ -4465,77 +4480,77 @@
         <v>360</v>
       </c>
       <c r="B59" t="s">
+        <v>350</v>
+      </c>
+      <c r="C59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" t="s">
         <v>361</v>
       </c>
-      <c r="C59" t="s">
-        <v>13</v>
-      </c>
-      <c r="D59" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" t="s">
+        <v>235</v>
+      </c>
+      <c r="I59" t="s">
         <v>362</v>
       </c>
-      <c r="G59" t="s">
-        <v>15</v>
-      </c>
-      <c r="H59" t="s">
-        <v>230</v>
-      </c>
-      <c r="I59" t="s">
+      <c r="J59" t="s">
         <v>363</v>
       </c>
-      <c r="J59" t="s">
+      <c r="K59" t="s">
         <v>364</v>
-      </c>
-      <c r="K59" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>365</v>
+      </c>
+      <c r="B60" t="s">
         <v>366</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" t="s">
         <v>367</v>
       </c>
-      <c r="C60" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" t="s">
+        <v>235</v>
+      </c>
+      <c r="I60" t="s">
         <v>368</v>
       </c>
-      <c r="G60" t="s">
-        <v>15</v>
-      </c>
-      <c r="H60" t="s">
-        <v>230</v>
-      </c>
-      <c r="I60" t="s">
+      <c r="J60" t="s">
         <v>369</v>
       </c>
-      <c r="J60" t="s">
+      <c r="K60" t="s">
         <v>370</v>
-      </c>
-      <c r="K60" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>371</v>
+      </c>
+      <c r="B61" t="s">
         <v>372</v>
-      </c>
-      <c r="B61" t="s">
-        <v>345</v>
       </c>
       <c r="C61" t="s">
         <v>13</v>
@@ -4553,7 +4568,7 @@
         <v>15</v>
       </c>
       <c r="H61" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I61" t="s">
         <v>374</v>
@@ -4570,7 +4585,7 @@
         <v>377</v>
       </c>
       <c r="B62" t="s">
-        <v>104</v>
+        <v>350</v>
       </c>
       <c r="C62" t="s">
         <v>13</v>
@@ -4588,94 +4603,94 @@
         <v>15</v>
       </c>
       <c r="H62" t="s">
+        <v>235</v>
+      </c>
+      <c r="I62" t="s">
         <v>379</v>
       </c>
-      <c r="I62" t="s">
+      <c r="J62" t="s">
         <v>380</v>
       </c>
-      <c r="J62" t="s">
+      <c r="K62" t="s">
         <v>381</v>
-      </c>
-      <c r="K62" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>382</v>
+      </c>
+      <c r="B63" t="s">
+        <v>109</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" t="s">
         <v>383</v>
       </c>
-      <c r="B63" t="s">
+      <c r="G63" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" t="s">
         <v>384</v>
       </c>
-      <c r="C63" t="s">
-        <v>13</v>
-      </c>
-      <c r="D63" t="s">
-        <v>13</v>
-      </c>
-      <c r="E63" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" t="s">
+      <c r="I63" t="s">
         <v>385</v>
       </c>
-      <c r="G63" t="s">
-        <v>15</v>
-      </c>
-      <c r="H63" t="s">
-        <v>217</v>
-      </c>
-      <c r="I63" t="s">
+      <c r="J63" t="s">
         <v>386</v>
       </c>
-      <c r="J63" t="s">
+      <c r="K63" t="s">
         <v>387</v>
-      </c>
-      <c r="K63" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>388</v>
+      </c>
+      <c r="B64" t="s">
         <v>389</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" t="s">
         <v>390</v>
       </c>
-      <c r="C64" t="s">
-        <v>13</v>
-      </c>
-      <c r="D64" t="s">
-        <v>13</v>
-      </c>
-      <c r="E64" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" t="s">
+        <v>222</v>
+      </c>
+      <c r="I64" t="s">
         <v>391</v>
       </c>
-      <c r="G64" t="s">
-        <v>15</v>
-      </c>
-      <c r="H64" t="s">
-        <v>217</v>
-      </c>
-      <c r="I64" t="s">
+      <c r="J64" t="s">
         <v>392</v>
       </c>
-      <c r="J64" t="s">
+      <c r="K64" t="s">
         <v>393</v>
-      </c>
-      <c r="K64" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>394</v>
+      </c>
+      <c r="B65" t="s">
         <v>395</v>
-      </c>
-      <c r="B65" t="s">
-        <v>384</v>
       </c>
       <c r="C65" t="s">
         <v>13</v>
@@ -4693,7 +4708,7 @@
         <v>15</v>
       </c>
       <c r="H65" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I65" t="s">
         <v>397</v>
@@ -4710,7 +4725,7 @@
         <v>400</v>
       </c>
       <c r="B66" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C66" t="s">
         <v>13</v>
@@ -4728,7 +4743,7 @@
         <v>15</v>
       </c>
       <c r="H66" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I66" t="s">
         <v>402</v>
@@ -4745,182 +4760,182 @@
         <v>405</v>
       </c>
       <c r="B67" t="s">
-        <v>34</v>
+        <v>395</v>
       </c>
       <c r="C67" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" t="s">
         <v>406</v>
       </c>
-      <c r="D67" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" t="s">
+        <v>222</v>
+      </c>
+      <c r="I67" t="s">
         <v>407</v>
       </c>
-      <c r="G67" t="s">
-        <v>15</v>
-      </c>
-      <c r="H67" t="s">
+      <c r="J67" t="s">
         <v>408</v>
       </c>
-      <c r="I67" t="s">
+      <c r="K67" t="s">
         <v>409</v>
-      </c>
-      <c r="J67" t="s">
-        <v>410</v>
-      </c>
-      <c r="K67" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>410</v>
+      </c>
+      <c r="B68" t="s">
+        <v>21</v>
+      </c>
+      <c r="C68" t="s">
+        <v>411</v>
+      </c>
+      <c r="D68" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" t="s">
         <v>412</v>
       </c>
-      <c r="B68" t="s">
-        <v>34</v>
-      </c>
-      <c r="C68" t="s">
+      <c r="G68" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" t="s">
         <v>413</v>
       </c>
-      <c r="D68" t="s">
-        <v>13</v>
-      </c>
-      <c r="E68" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" t="s">
+      <c r="I68" t="s">
         <v>414</v>
       </c>
-      <c r="G68" t="s">
-        <v>15</v>
-      </c>
-      <c r="H68" t="s">
-        <v>408</v>
-      </c>
-      <c r="I68" t="s">
+      <c r="J68" t="s">
         <v>415</v>
       </c>
-      <c r="J68" t="s">
+      <c r="K68" t="s">
         <v>416</v>
-      </c>
-      <c r="K68" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>417</v>
+      </c>
+      <c r="B69" t="s">
+        <v>21</v>
+      </c>
+      <c r="C69" t="s">
         <v>418</v>
       </c>
-      <c r="B69" t="s">
-        <v>34</v>
-      </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" t="s">
         <v>419</v>
       </c>
-      <c r="D69" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="G69" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" t="s">
+        <v>413</v>
+      </c>
+      <c r="I69" t="s">
         <v>420</v>
       </c>
-      <c r="F69" t="s">
+      <c r="J69" t="s">
         <v>421</v>
       </c>
-      <c r="G69" t="s">
-        <v>15</v>
-      </c>
-      <c r="H69" t="s">
+      <c r="K69" t="s">
         <v>422</v>
-      </c>
-      <c r="I69" t="s">
-        <v>423</v>
-      </c>
-      <c r="J69" t="s">
-        <v>424</v>
-      </c>
-      <c r="K69" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>423</v>
+      </c>
+      <c r="B70" t="s">
+        <v>21</v>
+      </c>
+      <c r="C70" t="s">
+        <v>424</v>
+      </c>
+      <c r="D70" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" t="s">
+        <v>425</v>
+      </c>
+      <c r="F70" t="s">
         <v>426</v>
       </c>
-      <c r="B70" t="s">
+      <c r="G70" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" t="s">
         <v>427</v>
       </c>
-      <c r="C70" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" t="s">
+      <c r="I70" t="s">
         <v>428</v>
       </c>
-      <c r="G70" t="s">
-        <v>15</v>
-      </c>
-      <c r="H70" t="s">
+      <c r="J70" t="s">
         <v>429</v>
       </c>
-      <c r="I70" t="s">
+      <c r="K70" t="s">
         <v>430</v>
-      </c>
-      <c r="J70" t="s">
-        <v>431</v>
-      </c>
-      <c r="K70" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>431</v>
+      </c>
+      <c r="B71" t="s">
+        <v>432</v>
+      </c>
+      <c r="C71" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" t="s">
         <v>433</v>
       </c>
-      <c r="B71" t="s">
+      <c r="G71" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" t="s">
         <v>434</v>
       </c>
-      <c r="C71" t="s">
-        <v>13</v>
-      </c>
-      <c r="D71" t="s">
-        <v>13</v>
-      </c>
-      <c r="E71" t="s">
-        <v>13</v>
-      </c>
-      <c r="F71" t="s">
+      <c r="I71" t="s">
         <v>435</v>
       </c>
-      <c r="G71" t="s">
-        <v>15</v>
-      </c>
-      <c r="H71" t="s">
-        <v>429</v>
-      </c>
-      <c r="I71" t="s">
+      <c r="J71" t="s">
         <v>436</v>
       </c>
-      <c r="J71" t="s">
+      <c r="K71" t="s">
         <v>437</v>
-      </c>
-      <c r="K71" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>438</v>
+      </c>
+      <c r="B72" t="s">
         <v>439</v>
-      </c>
-      <c r="B72" t="s">
-        <v>434</v>
       </c>
       <c r="C72" t="s">
         <v>13</v>
@@ -4938,7 +4953,7 @@
         <v>15</v>
       </c>
       <c r="H72" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="I72" t="s">
         <v>441</v>
@@ -4955,7 +4970,7 @@
         <v>444</v>
       </c>
       <c r="B73" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C73" t="s">
         <v>13</v>
@@ -4973,7 +4988,7 @@
         <v>15</v>
       </c>
       <c r="H73" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="I73" t="s">
         <v>446</v>
@@ -4990,95 +5005,95 @@
         <v>449</v>
       </c>
       <c r="B74" t="s">
+        <v>439</v>
+      </c>
+      <c r="C74" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" t="s">
         <v>450</v>
       </c>
-      <c r="C74" t="s">
-        <v>13</v>
-      </c>
-      <c r="D74" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" t="s">
-        <v>13</v>
-      </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" t="s">
+        <v>434</v>
+      </c>
+      <c r="I74" t="s">
         <v>451</v>
       </c>
-      <c r="G74" t="s">
-        <v>15</v>
-      </c>
-      <c r="H74" t="s">
-        <v>429</v>
-      </c>
-      <c r="I74" t="s">
+      <c r="J74" t="s">
         <v>452</v>
       </c>
-      <c r="J74" t="s">
+      <c r="K74" t="s">
         <v>453</v>
-      </c>
-      <c r="K74" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>454</v>
+      </c>
+      <c r="B75" t="s">
         <v>455</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" t="s">
         <v>456</v>
       </c>
-      <c r="C75" t="s">
-        <v>13</v>
-      </c>
-      <c r="D75" t="s">
-        <v>13</v>
-      </c>
-      <c r="E75" t="s">
-        <v>13</v>
-      </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" t="s">
+        <v>434</v>
+      </c>
+      <c r="I75" t="s">
         <v>457</v>
       </c>
-      <c r="G75" t="s">
-        <v>15</v>
-      </c>
-      <c r="H75" t="s">
+      <c r="J75" t="s">
         <v>458</v>
       </c>
-      <c r="I75" t="s">
+      <c r="K75" t="s">
         <v>459</v>
-      </c>
-      <c r="J75" t="s">
-        <v>460</v>
-      </c>
-      <c r="K75" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>460</v>
+      </c>
+      <c r="B76" t="s">
+        <v>461</v>
+      </c>
+      <c r="C76" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" t="s">
         <v>462</v>
       </c>
-      <c r="B76" t="s">
-        <v>456</v>
-      </c>
-      <c r="C76" t="s">
-        <v>13</v>
-      </c>
-      <c r="D76" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" t="s">
-        <v>13</v>
-      </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" t="s">
         <v>463</v>
-      </c>
-      <c r="G76" t="s">
-        <v>15</v>
-      </c>
-      <c r="H76" t="s">
-        <v>458</v>
       </c>
       <c r="I76" t="s">
         <v>464</v>
@@ -5095,7 +5110,7 @@
         <v>467</v>
       </c>
       <c r="B77" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C77" t="s">
         <v>13</v>
@@ -5113,7 +5128,7 @@
         <v>15</v>
       </c>
       <c r="H77" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I77" t="s">
         <v>469</v>
@@ -5130,7 +5145,7 @@
         <v>472</v>
       </c>
       <c r="B78" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C78" t="s">
         <v>13</v>
@@ -5148,7 +5163,7 @@
         <v>15</v>
       </c>
       <c r="H78" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I78" t="s">
         <v>474</v>
@@ -5157,15 +5172,15 @@
         <v>475</v>
       </c>
       <c r="K78" t="s">
-        <v>170</v>
+        <v>476</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B79" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C79" t="s">
         <v>13</v>
@@ -5177,30 +5192,30 @@
         <v>13</v>
       </c>
       <c r="F79" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G79" t="s">
         <v>15</v>
       </c>
       <c r="H79" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I79" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J79" t="s">
-        <v>13</v>
+        <v>480</v>
       </c>
       <c r="K79" t="s">
-        <v>479</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B80" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C80" t="s">
         <v>13</v>
@@ -5212,30 +5227,30 @@
         <v>13</v>
       </c>
       <c r="F80" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G80" t="s">
         <v>15</v>
       </c>
       <c r="H80" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I80" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J80" t="s">
         <v>13</v>
       </c>
       <c r="K80" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B81" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C81" t="s">
         <v>13</v>
@@ -5247,30 +5262,30 @@
         <v>13</v>
       </c>
       <c r="F81" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G81" t="s">
         <v>15</v>
       </c>
       <c r="H81" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I81" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J81" t="s">
         <v>13</v>
       </c>
       <c r="K81" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B82" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C82" t="s">
         <v>13</v>
@@ -5282,19 +5297,19 @@
         <v>13</v>
       </c>
       <c r="F82" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G82" t="s">
         <v>15</v>
       </c>
       <c r="H82" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I82" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J82" t="s">
-        <v>491</v>
+        <v>13</v>
       </c>
       <c r="K82" t="s">
         <v>492</v>
@@ -5305,7 +5320,7 @@
         <v>493</v>
       </c>
       <c r="B83" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C83" t="s">
         <v>13</v>
@@ -5323,7 +5338,7 @@
         <v>15</v>
       </c>
       <c r="H83" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I83" t="s">
         <v>495</v>
@@ -5340,7 +5355,7 @@
         <v>498</v>
       </c>
       <c r="B84" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C84" t="s">
         <v>13</v>
@@ -5358,24 +5373,24 @@
         <v>15</v>
       </c>
       <c r="H84" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I84" t="s">
         <v>500</v>
       </c>
       <c r="J84" t="s">
-        <v>13</v>
+        <v>501</v>
       </c>
       <c r="K84" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B85" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C85" t="s">
         <v>13</v>
@@ -5387,19 +5402,19 @@
         <v>13</v>
       </c>
       <c r="F85" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G85" t="s">
         <v>15</v>
       </c>
       <c r="H85" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I85" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J85" t="s">
-        <v>505</v>
+        <v>13</v>
       </c>
       <c r="K85" t="s">
         <v>506</v>
@@ -5410,7 +5425,7 @@
         <v>507</v>
       </c>
       <c r="B86" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C86" t="s">
         <v>13</v>
@@ -5428,7 +5443,7 @@
         <v>15</v>
       </c>
       <c r="H86" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I86" t="s">
         <v>509</v>
@@ -5445,7 +5460,7 @@
         <v>512</v>
       </c>
       <c r="B87" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C87" t="s">
         <v>13</v>
@@ -5463,24 +5478,24 @@
         <v>15</v>
       </c>
       <c r="H87" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I87" t="s">
         <v>514</v>
       </c>
       <c r="J87" t="s">
-        <v>13</v>
+        <v>515</v>
       </c>
       <c r="K87" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B88" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C88" t="s">
         <v>13</v>
@@ -5492,19 +5507,19 @@
         <v>13</v>
       </c>
       <c r="F88" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G88" t="s">
         <v>15</v>
       </c>
       <c r="H88" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I88" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J88" t="s">
-        <v>519</v>
+        <v>13</v>
       </c>
       <c r="K88" t="s">
         <v>520</v>
@@ -5515,7 +5530,7 @@
         <v>521</v>
       </c>
       <c r="B89" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C89" t="s">
         <v>13</v>
@@ -5533,7 +5548,7 @@
         <v>15</v>
       </c>
       <c r="H89" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I89" t="s">
         <v>523</v>
@@ -5550,7 +5565,7 @@
         <v>526</v>
       </c>
       <c r="B90" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C90" t="s">
         <v>13</v>
@@ -5568,24 +5583,24 @@
         <v>15</v>
       </c>
       <c r="H90" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I90" t="s">
         <v>528</v>
       </c>
       <c r="J90" t="s">
-        <v>13</v>
+        <v>529</v>
       </c>
       <c r="K90" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B91" t="s">
-        <v>104</v>
+        <v>461</v>
       </c>
       <c r="C91" t="s">
         <v>13</v>
@@ -5597,118 +5612,118 @@
         <v>13</v>
       </c>
       <c r="F91" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G91" t="s">
         <v>15</v>
       </c>
       <c r="H91" t="s">
-        <v>532</v>
+        <v>463</v>
       </c>
       <c r="I91" t="s">
         <v>533</v>
       </c>
       <c r="J91" t="s">
+        <v>13</v>
+      </c>
+      <c r="K91" t="s">
         <v>534</v>
-      </c>
-      <c r="K91" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>535</v>
+      </c>
+      <c r="B92" t="s">
+        <v>109</v>
+      </c>
+      <c r="C92" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" t="s">
         <v>536</v>
       </c>
-      <c r="B92" t="s">
+      <c r="G92" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" t="s">
         <v>537</v>
       </c>
-      <c r="C92" t="s">
-        <v>13</v>
-      </c>
-      <c r="D92" t="s">
-        <v>13</v>
-      </c>
-      <c r="E92" t="s">
-        <v>13</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="I92" t="s">
         <v>538</v>
       </c>
-      <c r="G92" t="s">
-        <v>15</v>
-      </c>
-      <c r="H92" t="s">
-        <v>323</v>
-      </c>
-      <c r="I92" t="s">
+      <c r="J92" t="s">
         <v>539</v>
       </c>
-      <c r="J92" t="s">
+      <c r="K92" t="s">
         <v>540</v>
-      </c>
-      <c r="K92" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>541</v>
+      </c>
+      <c r="B93" t="s">
         <v>542</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
+        <v>13</v>
+      </c>
+      <c r="D93" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93" t="s">
         <v>543</v>
       </c>
-      <c r="C93" t="s">
-        <v>13</v>
-      </c>
-      <c r="D93" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" t="s">
-        <v>13</v>
-      </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
+        <v>15</v>
+      </c>
+      <c r="H93" t="s">
+        <v>328</v>
+      </c>
+      <c r="I93" t="s">
         <v>544</v>
       </c>
-      <c r="G93" t="s">
-        <v>15</v>
-      </c>
-      <c r="H93" t="s">
+      <c r="J93" t="s">
         <v>545</v>
       </c>
-      <c r="I93" t="s">
+      <c r="K93" t="s">
         <v>546</v>
-      </c>
-      <c r="J93" t="s">
-        <v>547</v>
-      </c>
-      <c r="K93" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>547</v>
+      </c>
+      <c r="B94" t="s">
+        <v>548</v>
+      </c>
+      <c r="C94" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" t="s">
         <v>549</v>
       </c>
-      <c r="B94" t="s">
-        <v>333</v>
-      </c>
-      <c r="C94" t="s">
-        <v>13</v>
-      </c>
-      <c r="D94" t="s">
-        <v>13</v>
-      </c>
-      <c r="E94" t="s">
-        <v>13</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" t="s">
         <v>550</v>
-      </c>
-      <c r="G94" t="s">
-        <v>15</v>
-      </c>
-      <c r="H94" t="s">
-        <v>323</v>
       </c>
       <c r="I94" t="s">
         <v>551</v>
@@ -5725,42 +5740,42 @@
         <v>554</v>
       </c>
       <c r="B95" t="s">
+        <v>338</v>
+      </c>
+      <c r="C95" t="s">
+        <v>13</v>
+      </c>
+      <c r="D95" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" t="s">
         <v>555</v>
       </c>
-      <c r="C95" t="s">
-        <v>13</v>
-      </c>
-      <c r="D95" t="s">
-        <v>13</v>
-      </c>
-      <c r="E95" t="s">
-        <v>13</v>
-      </c>
-      <c r="F95" t="s">
+      <c r="G95" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" t="s">
+        <v>328</v>
+      </c>
+      <c r="I95" t="s">
         <v>556</v>
       </c>
-      <c r="G95" t="s">
-        <v>15</v>
-      </c>
-      <c r="H95" t="s">
-        <v>323</v>
-      </c>
-      <c r="I95" t="s">
+      <c r="J95" t="s">
         <v>557</v>
       </c>
-      <c r="J95" t="s">
+      <c r="K95" t="s">
         <v>558</v>
-      </c>
-      <c r="K95" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>559</v>
+      </c>
+      <c r="B96" t="s">
         <v>560</v>
-      </c>
-      <c r="B96" t="s">
-        <v>537</v>
       </c>
       <c r="C96" t="s">
         <v>13</v>
@@ -5778,7 +5793,7 @@
         <v>15</v>
       </c>
       <c r="H96" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="I96" t="s">
         <v>562</v>
@@ -5795,7 +5810,7 @@
         <v>565</v>
       </c>
       <c r="B97" t="s">
-        <v>104</v>
+        <v>542</v>
       </c>
       <c r="C97" t="s">
         <v>13</v>
@@ -5813,7 +5828,7 @@
         <v>15</v>
       </c>
       <c r="H97" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="I97" t="s">
         <v>567</v>
@@ -5830,7 +5845,7 @@
         <v>570</v>
       </c>
       <c r="B98" t="s">
-        <v>543</v>
+        <v>109</v>
       </c>
       <c r="C98" t="s">
         <v>13</v>
@@ -5848,7 +5863,7 @@
         <v>15</v>
       </c>
       <c r="H98" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="I98" t="s">
         <v>572</v>
@@ -5865,42 +5880,42 @@
         <v>575</v>
       </c>
       <c r="B99" t="s">
+        <v>548</v>
+      </c>
+      <c r="C99" t="s">
+        <v>13</v>
+      </c>
+      <c r="D99" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" t="s">
         <v>576</v>
       </c>
-      <c r="C99" t="s">
-        <v>13</v>
-      </c>
-      <c r="D99" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" t="s">
-        <v>13</v>
-      </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" t="s">
+        <v>328</v>
+      </c>
+      <c r="I99" t="s">
         <v>577</v>
       </c>
-      <c r="G99" t="s">
-        <v>15</v>
-      </c>
-      <c r="H99" t="s">
-        <v>545</v>
-      </c>
-      <c r="I99" t="s">
+      <c r="J99" t="s">
         <v>578</v>
       </c>
-      <c r="J99" t="s">
+      <c r="K99" t="s">
         <v>579</v>
-      </c>
-      <c r="K99" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>580</v>
+      </c>
+      <c r="B100" t="s">
         <v>581</v>
-      </c>
-      <c r="B100" t="s">
-        <v>543</v>
       </c>
       <c r="C100" t="s">
         <v>13</v>
@@ -5918,7 +5933,7 @@
         <v>15</v>
       </c>
       <c r="H100" t="s">
-        <v>323</v>
+        <v>550</v>
       </c>
       <c r="I100" t="s">
         <v>583</v>
@@ -5935,7 +5950,7 @@
         <v>586</v>
       </c>
       <c r="B101" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="C101" t="s">
         <v>13</v>
@@ -5953,7 +5968,7 @@
         <v>15</v>
       </c>
       <c r="H101" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="I101" t="s">
         <v>588</v>
@@ -5970,42 +5985,42 @@
         <v>591</v>
       </c>
       <c r="B102" t="s">
+        <v>542</v>
+      </c>
+      <c r="C102" t="s">
+        <v>13</v>
+      </c>
+      <c r="D102" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" t="s">
         <v>592</v>
       </c>
-      <c r="C102" t="s">
-        <v>13</v>
-      </c>
-      <c r="D102" t="s">
-        <v>13</v>
-      </c>
-      <c r="E102" t="s">
-        <v>13</v>
-      </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
+        <v>15</v>
+      </c>
+      <c r="H102" t="s">
+        <v>328</v>
+      </c>
+      <c r="I102" t="s">
         <v>593</v>
       </c>
-      <c r="G102" t="s">
-        <v>15</v>
-      </c>
-      <c r="H102" t="s">
-        <v>323</v>
-      </c>
-      <c r="I102" t="s">
+      <c r="J102" t="s">
         <v>594</v>
       </c>
-      <c r="J102" t="s">
+      <c r="K102" t="s">
         <v>595</v>
-      </c>
-      <c r="K102" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>596</v>
+      </c>
+      <c r="B103" t="s">
         <v>597</v>
-      </c>
-      <c r="B103" t="s">
-        <v>543</v>
       </c>
       <c r="C103" t="s">
         <v>13</v>
@@ -6023,7 +6038,7 @@
         <v>15</v>
       </c>
       <c r="H103" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="I103" t="s">
         <v>599</v>
@@ -6040,7 +6055,7 @@
         <v>602</v>
       </c>
       <c r="B104" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="C104" t="s">
         <v>13</v>
@@ -6058,42 +6073,42 @@
         <v>15</v>
       </c>
       <c r="H104" t="s">
+        <v>328</v>
+      </c>
+      <c r="I104" t="s">
         <v>604</v>
       </c>
-      <c r="I104" t="s">
+      <c r="J104" t="s">
         <v>605</v>
       </c>
-      <c r="J104" t="s">
+      <c r="K104" t="s">
         <v>606</v>
-      </c>
-      <c r="K104" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>607</v>
+      </c>
+      <c r="B105" t="s">
+        <v>542</v>
+      </c>
+      <c r="C105" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" t="s">
+        <v>13</v>
+      </c>
+      <c r="F105" t="s">
         <v>608</v>
       </c>
-      <c r="B105" t="s">
-        <v>543</v>
-      </c>
-      <c r="C105" t="s">
-        <v>13</v>
-      </c>
-      <c r="D105" t="s">
-        <v>13</v>
-      </c>
-      <c r="E105" t="s">
-        <v>13</v>
-      </c>
-      <c r="F105" t="s">
+      <c r="G105" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" t="s">
         <v>609</v>
-      </c>
-      <c r="G105" t="s">
-        <v>15</v>
-      </c>
-      <c r="H105" t="s">
-        <v>545</v>
       </c>
       <c r="I105" t="s">
         <v>610</v>
@@ -6110,7 +6125,7 @@
         <v>613</v>
       </c>
       <c r="B106" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C106" t="s">
         <v>13</v>
@@ -6128,7 +6143,7 @@
         <v>15</v>
       </c>
       <c r="H106" t="s">
-        <v>323</v>
+        <v>550</v>
       </c>
       <c r="I106" t="s">
         <v>615</v>
@@ -6145,7 +6160,7 @@
         <v>618</v>
       </c>
       <c r="B107" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="C107" t="s">
         <v>13</v>
@@ -6163,7 +6178,7 @@
         <v>15</v>
       </c>
       <c r="H107" t="s">
-        <v>604</v>
+        <v>328</v>
       </c>
       <c r="I107" t="s">
         <v>620</v>
@@ -6180,7 +6195,7 @@
         <v>623</v>
       </c>
       <c r="B108" t="s">
-        <v>104</v>
+        <v>542</v>
       </c>
       <c r="C108" t="s">
         <v>13</v>
@@ -6198,7 +6213,7 @@
         <v>15</v>
       </c>
       <c r="H108" t="s">
-        <v>379</v>
+        <v>609</v>
       </c>
       <c r="I108" t="s">
         <v>625</v>
@@ -6215,7 +6230,7 @@
         <v>628</v>
       </c>
       <c r="B109" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C109" t="s">
         <v>13</v>
@@ -6233,7 +6248,7 @@
         <v>15</v>
       </c>
       <c r="H109" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="I109" t="s">
         <v>630</v>
@@ -6250,7 +6265,7 @@
         <v>633</v>
       </c>
       <c r="B110" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C110" t="s">
         <v>13</v>
@@ -6268,7 +6283,7 @@
         <v>15</v>
       </c>
       <c r="H110" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="I110" t="s">
         <v>635</v>
@@ -6285,7 +6300,7 @@
         <v>638</v>
       </c>
       <c r="B111" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C111" t="s">
         <v>13</v>
@@ -6303,7 +6318,7 @@
         <v>15</v>
       </c>
       <c r="H111" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="I111" t="s">
         <v>640</v>
@@ -6320,7 +6335,7 @@
         <v>643</v>
       </c>
       <c r="B112" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C112" t="s">
         <v>13</v>
@@ -6338,7 +6353,7 @@
         <v>15</v>
       </c>
       <c r="H112" t="s">
-        <v>532</v>
+        <v>384</v>
       </c>
       <c r="I112" t="s">
         <v>645</v>
@@ -6355,7 +6370,7 @@
         <v>648</v>
       </c>
       <c r="B113" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C113" t="s">
         <v>13</v>
@@ -6373,7 +6388,7 @@
         <v>15</v>
       </c>
       <c r="H113" t="s">
-        <v>379</v>
+        <v>537</v>
       </c>
       <c r="I113" t="s">
         <v>650</v>
@@ -6390,51 +6405,51 @@
         <v>653</v>
       </c>
       <c r="B114" t="s">
+        <v>109</v>
+      </c>
+      <c r="C114" t="s">
+        <v>13</v>
+      </c>
+      <c r="D114" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" t="s">
         <v>654</v>
       </c>
-      <c r="C114" t="s">
-        <v>406</v>
-      </c>
-      <c r="D114" t="s">
-        <v>13</v>
-      </c>
-      <c r="E114" t="s">
+      <c r="G114" t="s">
+        <v>15</v>
+      </c>
+      <c r="H114" t="s">
+        <v>384</v>
+      </c>
+      <c r="I114" t="s">
         <v>655</v>
       </c>
-      <c r="F114" t="s">
+      <c r="J114" t="s">
         <v>656</v>
       </c>
-      <c r="G114" t="s">
-        <v>15</v>
-      </c>
-      <c r="H114" t="s">
-        <v>422</v>
-      </c>
-      <c r="I114" t="s">
+      <c r="K114" t="s">
         <v>657</v>
-      </c>
-      <c r="J114" t="s">
-        <v>658</v>
-      </c>
-      <c r="K114" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>658</v>
+      </c>
+      <c r="B115" t="s">
+        <v>659</v>
+      </c>
+      <c r="C115" t="s">
+        <v>411</v>
+      </c>
+      <c r="D115" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" t="s">
         <v>660</v>
-      </c>
-      <c r="B115" t="s">
-        <v>654</v>
-      </c>
-      <c r="C115" t="s">
-        <v>413</v>
-      </c>
-      <c r="D115" t="s">
-        <v>13</v>
-      </c>
-      <c r="E115" t="s">
-        <v>655</v>
       </c>
       <c r="F115" t="s">
         <v>661</v>
@@ -6443,7 +6458,7 @@
         <v>15</v>
       </c>
       <c r="H115" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="I115" t="s">
         <v>662</v>
@@ -6460,34 +6475,69 @@
         <v>665</v>
       </c>
       <c r="B116" t="s">
+        <v>659</v>
+      </c>
+      <c r="C116" t="s">
+        <v>418</v>
+      </c>
+      <c r="D116" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" t="s">
+        <v>660</v>
+      </c>
+      <c r="F116" t="s">
         <v>666</v>
       </c>
-      <c r="C116" t="s">
+      <c r="G116" t="s">
+        <v>15</v>
+      </c>
+      <c r="H116" t="s">
+        <v>427</v>
+      </c>
+      <c r="I116" t="s">
         <v>667</v>
       </c>
-      <c r="D116" t="s">
-        <v>13</v>
-      </c>
-      <c r="E116" t="s">
+      <c r="J116" t="s">
         <v>668</v>
       </c>
-      <c r="F116" t="s">
+      <c r="K116" t="s">
         <v>669</v>
       </c>
-      <c r="G116" t="s">
-        <v>15</v>
-      </c>
-      <c r="H116" t="s">
-        <v>422</v>
-      </c>
-      <c r="I116" t="s">
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>670</v>
       </c>
-      <c r="J116" t="s">
+      <c r="B117" t="s">
         <v>671</v>
       </c>
-      <c r="K116" t="s">
+      <c r="C117" t="s">
         <v>672</v>
+      </c>
+      <c r="D117" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" t="s">
+        <v>673</v>
+      </c>
+      <c r="F117" t="s">
+        <v>674</v>
+      </c>
+      <c r="G117" t="s">
+        <v>15</v>
+      </c>
+      <c r="H117" t="s">
+        <v>427</v>
+      </c>
+      <c r="I117" t="s">
+        <v>675</v>
+      </c>
+      <c r="J117" t="s">
+        <v>676</v>
+      </c>
+      <c r="K117" t="s">
+        <v>677</v>
       </c>
     </row>
   </sheetData>
